--- a/agrra_monitoring/data_raw/ATG_NPA_2025/Calculated/FishBiomass.xlsx
+++ b/agrra_monitoring/data_raw/ATG_NPA_2025/Calculated/FishBiomass.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\AGRRA\Sent Product Files\products\Calculated\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\AGRRA Group Work\Data Product Fix\Ruleo\NDNP2025\Calculated\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED21CBA-686E-40DD-83D0-250C5CCC4418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC134CD-D893-4F60-AFE6-A0F7E9747DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-45" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="TermsOfUse" sheetId="24" r:id="rId1"/>
+    <sheet name="TermsOfUse" sheetId="25" r:id="rId1"/>
     <sheet name="Metadata" sheetId="1" r:id="rId2"/>
     <sheet name="Overall" sheetId="2" r:id="rId3"/>
     <sheet name="tACAN" sheetId="3" r:id="rId4"/>
@@ -38,7 +38,7 @@
     <sheet name="tTETR" sheetId="22" r:id="rId23"/>
     <sheet name="UNKN" sheetId="23" r:id="rId24"/>
   </sheets>
-  <calcPr calcId="999999"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -2339,12 +2339,40 @@
     <t>TETRstd</t>
   </si>
   <si>
-    <t>Created: 2025 Aug 8</t>
-  </si>
-  <si>
-    <t>Version 1.0</t>
-  </si>
-  <si>
+    <t>Created: 2026 May 29</t>
+  </si>
+  <si>
+    <t>AGRRA Terms of Data Service</t>
+  </si>
+  <si>
+    <t>The Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program champions coral reef conservation and empowers those who protect these diverse ecosystems. We are an international collaboration of scientists, managers, and supporters aimed at improving the regional condition of reefs in the Western Atlantic and Gulf of Mexico. For 25 years, AGRRA has used an innovative regional approach to examine the condition of reef-building corals, algae, and fishes, and support the conservation of coral reef ecosystems. We curate and distribute data, research and educational materials that support this mission. For more information, visit www.agrra.org or email info@agrra.org.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">AGRRA’s goal is to provide data contributors access to the AGRRA data platform, which provides: 
+a)	a standardized way to enter coral reef monitoring data with built in quality controls,
+b)	an efficient way to process data and visualize data through interactive graphics,
+c)	synthesized data products provided as RAW data and Calculated Products, and 
+d)	a centralized and secure place to manage and store data.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Ownership &amp; Intellectual Property</t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -2354,23 +2382,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Date produced: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Data in this country batch were produced in collaboration with the batch owner: Ruleo Camacho. These data products are in draft form and are under review. Prior to data use, you need to accept the Terms and Conditions in the AGRRA Data License below. In addition, permission to distribute data must follow any data agreements required by the batch owner and/or individual surveyors who submitted data prior to use. </t>
-    </r>
-  </si>
-  <si>
-    <t>The Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program champions coral reef conservation and empowers those who protect these diverse ecosystems. We are an international collaboration of scientists, managers, and supporters aimed at improving the regional condition of reefs in the Western Atlantic and Gulf of Mexico. For 25 years, AGRRA has used an innovative regional approach to examine the condition of reef-building corals, algae and fishes and support the conservation of coral reef ecosystems. We curate and distribute data, research and educational materials that support this mission. For more information, visit www.agrra.org or email info@agrra.org.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Conditions of Use of AGRRA Data Products
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -2379,7 +2391,330 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">In order to use the AGRRA dataset, you need to accept the Terms and Conditions in the AGRRA Data License below.
+      <t xml:space="preserve">•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Original Observations:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> The raw data collected during surveys remains the intellectual property of the original data collectors and their respective organizations.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Methodology &amp; Systems: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">All protocols (Benthic, Coral, Fish), platform systems, AGRRA content, and related tools remain the intellectual property of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ocean Research &amp; Education Foundation, Inc. (ORE)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AGRRA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">, and their licensors, as applicable.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Processed Metrics: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">The calculated metrics, custom-coded logic, and standardized protocols used to generate these spreadsheets are the proprietary property of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AGRRA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> and the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ocean Research &amp; Education Foundation (ORE)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">User Content: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Users retain ownership of data, images, and other content they submit, but grant AGRRA the rights needed to store, process, share, and display that content in accordance with these terms.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. Data Sharing &amp; Privacy Publication Protocol
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">AGRRA is committed to protecting the privacy of the Data Contributors with respect to their data batches and offers three privacy options for each data batch:
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Data Batch Privacy Options: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Data Batches may be designated as Private, Public Summary, or Public. Some batch metadata may remain publicly visible to support transparency and attribution.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Accounts &amp; Security:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Data Contributors are responsible for their accounts, passwords, and all activity under their accounts, and must promptly report any suspected unauthorized access.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+3. Permitted Uses</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+•	Non-Commercial Use:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Data Contributors and Third-party Users (with permission) are licensed to use these materials and datasets for research, education, conservation, and other non-commercial purposes.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Commercial Use:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Commercial use, sale, or redistribution of AGRRA materials, datasets, or API outputs requires prior written permission.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Lawful and Responsible Use:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> All users must comply with applicable laws and must not misuse, disrupt, alter, scrape, or interfere with the platform, its software, security, or other users.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+4. Citation &amp; Acknowledgment
 </t>
     </r>
     <r>
@@ -2391,7 +2726,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>AGRRA Data License and Data Use Agreements</t>
+      <t>A. Guidance for Original Data Contributors</t>
     </r>
     <r>
       <rPr>
@@ -2400,7 +2735,167 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
-By accessing and using any of the datasets distributed by AGRRA, you acknowledge that you have read, understood, and agree to comply with the terms and conditions contained within this agreement. A Data Use Agreement (DUA) must be entered into before there is any use or distribution of a data set to an outside entity. AGRRA may amend these terms and conditions at any time. Your continued use of this data constitutes acceptance of the terms and conditions stated at the time of your use. You should contact AGRRA to determine the current terms and conditions to which you are bound.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>How to cite your data:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> When publishing, presenting, or otherwise sharing analyses based on your own contributed dataset, please cite the dataset using the suggested AGRRA format: [Surveyor Names/Organization], [Country] ([Year]). [Dataset Name/Region]. In: Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform, [Protocol Version Number] [Data Product Name]. [URL/DOI]. Accessed [Date].
+                o   Examples
+                         ▪For a specific survey: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Smith, J. &amp; Reef Care Bahamas, Bahamas (2024). New Providence Benthic Surveys. In: Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform, v5.2 Coral &amp; Benthic Data. www.agrra.org. Accessed May 14, 2026.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+                         ▪For an aggregated country-level report: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Belize Fisheries Department &amp; Healthy Reefs Initiative, Belize (2025). 2025 National Monitoring Data. In: Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform. www.agrra.org. Accessed May 2026.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>How to acknowledge AGRRA:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> In all publications and presentations using your contributed data, please acknowledge AGRRA as the platform that curates, manages, and provides access to the dataset.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Suggested acknowledgment language:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> "We acknowledge (or thank) the Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform for curating and providing access to the dataset used in this work."
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Collaboration:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Contributors are encouraged to remain available for collaboration when their expertise may strengthen data interpretation or publication.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Notification of use:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Please share an electronic copy of any final reports, publications, or presentations with AGRRA curated data to data@agrra.org.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -2412,7 +2907,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Data Permissions and Proprietary Rights to Content</t>
+      <t>B. Guidance for Third-Party Data Users</t>
     </r>
     <r>
       <rPr>
@@ -2421,8 +2916,8 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
-All datasets are the property of AGRRA and/or its affiliates, unless otherwise noted. With permission and DUA, you may use these datasets for non-commercial purposes, including research, education, presentations, and non-commercial publications. You understand and agree that you may not copy, reproduce, distribute or create derivative works for other purposes, without prior, written authorization from the AGRRA Project Leader. When using or publishing any parts of these datasets, proper acknowledgement of AGRRA and original source(s), is required.
-</t>
+Third-party users (not original data collectors) who would like to use an AGRRA data batch should first contact and obtain permission from the original data contributor and/or AGRRA at data@agrra.org. Once permission is granted, third-party users who utilize AGRRA-hosted data for research, presentations, reports, or publications shall give appropriate credit to both the original data contributors and AGRRA. The guidance below explains how to cite the original dataset and how to acknowledge AGRRA as the data platform.
+•	</t>
     </r>
     <r>
       <rPr>
@@ -2433,7 +2928,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Limitation of Liability</t>
+      <t xml:space="preserve">How to cite original data contributors: </t>
     </r>
     <r>
       <rPr>
@@ -2441,9 +2936,8 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">
-AGRRA makes reasonable efforts to provide accurate data and information through its website, database, and other channels. Nevertheless, you understand and agree that AGRRA shall not be liable for any loss or damage resulting from any use of, or inability to use, this data, or resulting from any errors or omissions in the data content.
-</t>
+      <t xml:space="preserve">Cite the dataset using the names of the original surveyors, organizations, country, year, and dataset title, following the AGRRA dataset citation format. AGRRA can provide guidance on the appropriate citation for the specific dataset used.
+•	</t>
     </r>
     <r>
       <rPr>
@@ -2454,7 +2948,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Data Citation </t>
+      <t>How to acknowledge AGRRA:</t>
     </r>
     <r>
       <rPr>
@@ -2462,9 +2956,8 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">
-For any use of AGRRA data or datasets managed by AGRRA, or for general reference to the project in peer-reviewed literature, use the citation specified in the data use policy or for general citation use the following format below to cite data retrieved from the AGRRA website or AGRRA database manager. 
-</t>
+      <t xml:space="preserve"> In addition to citing the original dataset, acknowledge the Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform as the system that curates, manages, and provides access to the data.
+•	</t>
     </r>
     <r>
       <rPr>
@@ -2475,7 +2968,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Citation:</t>
+      <t xml:space="preserve">Suggested acknowledgment language: </t>
     </r>
     <r>
       <rPr>
@@ -2483,8 +2976,8 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve"> AGRRA. 2024. Atlantic and Gulf Rapid Reef Assessment (AGRRA): An online database of AGRRA coral reef survey data. Available: http://agrra.org. (Accessed: Date [e.g., March 10, 2024]).
-</t>
+      <t xml:space="preserve">"We thank the original data contributors [insert surveyor and/or organization names, where available] and acknowledge the Atlantic and Gulf Rapid Reef Assessment (AGRRA) Program Data Platform for curating and providing access to the dataset used in this work."
+•	</t>
     </r>
     <r>
       <rPr>
@@ -2495,7 +2988,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Acknowledgement:</t>
+      <t>Direct contact and collaboration:</t>
     </r>
     <r>
       <rPr>
@@ -2503,11 +2996,30 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve"> For general data, use: “We thank the following data providers: Atlantic Gulf Rapid Reef Assessment (AGRRA) contributors and data managers…”. Where noted, individual data contributors should be included in acknowledgments. 
+      <t xml:space="preserve"> Third-party users are encouraged to contact the original data collectors to discuss collaboration or co-authorship, clarify interpretation, and share findings, where appropriate.
 </t>
     </r>
-  </si>
-  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+5. Liability &amp; Compliance
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">•	</t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -2517,7 +3029,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Data Use Policy</t>
+      <t>Data Integrity:</t>
     </r>
     <r>
       <rPr>
@@ -2525,19 +3037,9 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">
-Data collected under the auspices of AGRRA are available to the public after primary publication, or at most two years after the completion of the study unless proprietary restrictions are warranted. Request for the use of AGRRA data is to be made in writing and is subject to acceptance of the following conditions:
-1. The user agrees to provide valid name and contact information prior to requesting or downloading online data. This information will be used to ensure data agreements are in place, to contact the user in case of changes to the data, and may also be used by data set authors and AGRRA project administrators to document data usage.
-2. The user agrees to cite the data set author (if stated) and AGRRA in all publications in which the data are used, as per the instructions in “Data Citation”. 
-3. The user agrees to provide one copy of any manuscript based on AGRRA data to the AGRRA or data set author (if specified) prior to submitting it for peer-reviewed publication.
-4. The user also agrees to send one electronic copy or reports or publication (pdf format) to: data@agrra.org and gis@agrra.org. 
-5. Users are prohibited from selling or redistributing any data provided by AGRRA without explicit prior permission.
-6. If specified, users are to contact original investigators or data contributors responsible for data prior to data use, and where appropriate, are encouraged to consider collaboration and/or co-authorship with original investigators.
-7. Extensive efforts are made to ensure that data products are accurate and up to date, but the authors and AGRRA will not take responsibility for any errors that may exist in data provided. The user assumes all responsibility for errors in analysis or judgment resulting from use of the data.
-8. Any violation of the terms of this agreement will result in immediate forfeiture of the data and loss of access privileges to other AGRRA data sets.  </t>
+      <t xml:space="preserve"> AGRRA works diligently to maintain data accuracy; however, Data Contributors and Third-Party users are responsible for their own analyses, interpretations, and resulting conclusions.
+•	</t>
     </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -2547,7 +3049,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Format of Data:</t>
+      <t>No Warranty:</t>
     </r>
     <r>
       <rPr>
@@ -2555,8 +3057,71 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve"> Original data is submitted into the data portal by surveyors trained in the AGRRA method to maintain data accuracy and consistency. AGRRA provides data products as raw products and as calculated products. Note these are draft data products from the beta version of the new AGRRA data portal (2024) and are currently in review. AGRRA reserves the right to update data products as needed.  Contact AGRRA if you have questions.</t>
+      <t xml:space="preserve"> The platform, data, and related content are provided “as is” and “as available,” without guarantees of accuracy, availability, security, or fitness for a particular purpose.
+•	</t>
     </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Limitation of Liability:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> AGRRA and its operators are not liable for indirect, incidental, consequential, or data-loss-related damages arising from the use of the platform.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Access Review: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">If these terms are not followed, AGRRA reserves the right to review, suspend, modify, or terminate access privileges or service availability as appropriate.
+•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Changes &amp; Governing Law:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> AGRRA may update these terms from time to time; continued use represents acceptance. </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">           </t>
   </si>
   <si>
     <r>
@@ -2580,23 +3145,30 @@
     </r>
   </si>
   <si>
+    <t>Version 1.0</t>
+  </si>
+  <si>
+    <t>Data provided in these country batches were produced in collaboration with the batch owner: Ruleo Camacho. Prior to data use, you need to accept the Terms and Conditions in the AGRRA Terms of Data Service below. In addition, permission to distribute data must follow any data agreements required by the batch owner and/or individual surveyors who submitted data prior to use.</t>
+  </si>
+  <si>
     <r>
       <rPr>
+        <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
-      <t>©</t>
+      <t>Format of Data:</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Ocean Research and Education Foundation</t>
+      <t xml:space="preserve"> Original data is submitted into the data portal by surveyors trained in the AGRRA method to maintain data accuracy and consistency. AGRRA provides data products as raw products and as calculated products. AGRRA reserves the right to update data products as needed.  Contact AGRRA if you have questions.</t>
     </r>
   </si>
 </sst>
@@ -2607,11 +3179,18 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0#"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2635,16 +3214,35 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2667,7 +3265,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -2685,6 +3283,66 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -2694,7 +3352,22 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -2817,16 +3490,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -2845,13 +3519,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2860,117 +3537,105 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{5D7BABE0-6B0A-4843-ACEA-A17A9E0B51FE}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{AB315437-7991-4A0C-92F3-16553FE861FE}"/>
+    <cellStyle name="Normal 2 2" xfId="2" xr:uid="{6CAD0BA8-A84A-46DE-88EE-F8A924AD04C3}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
@@ -2983,61 +3648,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>257176</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>180976</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>322132</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>123826</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A8D6114-1262-4BCC-8181-02B84D7192A6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6276976" y="180976"/>
-          <a:ext cx="2655756" cy="2038350"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3326,1051 +3936,1601 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91C72126-DBEC-406B-B7CC-5A813C2A2D71}">
-  <dimension ref="A1:W78"/>
-  <sheetFormatPr defaultColWidth="9.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{814185C5-E9A0-48E9-B861-34BC43904283}">
+  <dimension ref="A1:X70"/>
+  <sheetFormatPr defaultColWidth="9.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="16" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" style="16" customWidth="1"/>
-    <col min="3" max="16384" width="9.7109375" style="16"/>
+    <col min="2" max="2" width="11.26953125" style="16" customWidth="1"/>
+    <col min="3" max="16384" width="9.7265625" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" s="15" t="s">
         <v>756</v>
       </c>
       <c r="B1" s="15"/>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
+        <v>762</v>
+      </c>
+      <c r="B2" s="15"/>
+    </row>
+    <row r="4" spans="1:23" ht="19.5" x14ac:dyDescent="0.45">
+      <c r="A4" s="17" t="s">
         <v>757</v>
       </c>
-      <c r="B2" s="15"/>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="18"/>
+      <c r="R4" s="18"/>
+      <c r="S4" s="18"/>
+      <c r="T4" s="18"/>
+      <c r="U4" s="18"/>
+      <c r="V4" s="18"/>
+      <c r="W4" s="18"/>
+    </row>
+    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A6" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="20"/>
+      <c r="U6" s="20"/>
+      <c r="V6" s="20"/>
+      <c r="W6" s="21"/>
+    </row>
+    <row r="7" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="22"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
+      <c r="S7" s="23"/>
+      <c r="T7" s="23"/>
+      <c r="U7" s="23"/>
+      <c r="V7" s="23"/>
+      <c r="W7" s="24"/>
+    </row>
+    <row r="8" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:23" ht="53.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="25" t="s">
         <v>758</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
-      <c r="R13" s="17"/>
-      <c r="S13" s="17"/>
-      <c r="T13" s="17"/>
-      <c r="U13" s="17"/>
-      <c r="V13" s="17"/>
-      <c r="W13" s="17"/>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="17"/>
-      <c r="S14" s="17"/>
-      <c r="T14" s="17"/>
-      <c r="U14" s="17"/>
-      <c r="V14" s="17"/>
-      <c r="W14" s="17"/>
-    </row>
-    <row r="15" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:23" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="26"/>
+      <c r="R9" s="26"/>
+      <c r="S9" s="26"/>
+      <c r="T9" s="26"/>
+      <c r="U9" s="26"/>
+      <c r="V9" s="26"/>
+      <c r="W9" s="27"/>
+    </row>
+    <row r="10" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="28" t="s">
         <v>759</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="19"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="19"/>
-      <c r="U16" s="19"/>
-      <c r="V16" s="19"/>
-      <c r="W16" s="20"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="29"/>
+      <c r="R10" s="29"/>
+      <c r="S10" s="29"/>
+      <c r="T10" s="29"/>
+      <c r="U10" s="29"/>
+      <c r="V10" s="29"/>
+      <c r="W10" s="30"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A11" s="31"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="32"/>
+      <c r="N11" s="32"/>
+      <c r="O11" s="32"/>
+      <c r="P11" s="32"/>
+      <c r="Q11" s="32"/>
+      <c r="R11" s="32"/>
+      <c r="S11" s="32"/>
+      <c r="T11" s="32"/>
+      <c r="U11" s="32"/>
+      <c r="V11" s="32"/>
+      <c r="W11" s="33"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A12" s="31"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="32"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="32"/>
+      <c r="P12" s="32"/>
+      <c r="Q12" s="32"/>
+      <c r="R12" s="32"/>
+      <c r="S12" s="32"/>
+      <c r="T12" s="32"/>
+      <c r="U12" s="32"/>
+      <c r="V12" s="32"/>
+      <c r="W12" s="33"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A13" s="31"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="32"/>
+      <c r="S13" s="32"/>
+      <c r="T13" s="32"/>
+      <c r="U13" s="32"/>
+      <c r="V13" s="32"/>
+      <c r="W13" s="33"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A14" s="31"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="32"/>
+      <c r="M14" s="32"/>
+      <c r="N14" s="32"/>
+      <c r="O14" s="32"/>
+      <c r="P14" s="32"/>
+      <c r="Q14" s="32"/>
+      <c r="R14" s="32"/>
+      <c r="S14" s="32"/>
+      <c r="T14" s="32"/>
+      <c r="U14" s="32"/>
+      <c r="V14" s="32"/>
+      <c r="W14" s="33"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A15" s="31"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
+      <c r="T15" s="32"/>
+      <c r="U15" s="32"/>
+      <c r="V15" s="32"/>
+      <c r="W15" s="33"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A16" s="31"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="32"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="32"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="32"/>
+      <c r="S16" s="32"/>
+      <c r="T16" s="32"/>
+      <c r="U16" s="32"/>
+      <c r="V16" s="32"/>
+      <c r="W16" s="33"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A17" s="31"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="32"/>
+      <c r="L17" s="32"/>
+      <c r="M17" s="32"/>
+      <c r="N17" s="32"/>
+      <c r="O17" s="32"/>
+      <c r="P17" s="32"/>
+      <c r="Q17" s="32"/>
+      <c r="R17" s="32"/>
+      <c r="S17" s="32"/>
+      <c r="T17" s="32"/>
+      <c r="U17" s="32"/>
+      <c r="V17" s="32"/>
+      <c r="W17" s="33"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A18" s="31"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="32"/>
+      <c r="L18" s="32"/>
+      <c r="M18" s="32"/>
+      <c r="N18" s="32"/>
+      <c r="O18" s="32"/>
+      <c r="P18" s="32"/>
+      <c r="Q18" s="32"/>
+      <c r="R18" s="32"/>
+      <c r="S18" s="32"/>
+      <c r="T18" s="32"/>
+      <c r="U18" s="32"/>
+      <c r="V18" s="32"/>
+      <c r="W18" s="33"/>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A19" s="31"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="32"/>
+      <c r="N19" s="32"/>
+      <c r="O19" s="32"/>
+      <c r="P19" s="32"/>
+      <c r="Q19" s="32"/>
+      <c r="R19" s="32"/>
+      <c r="S19" s="32"/>
+      <c r="T19" s="32"/>
+      <c r="U19" s="32"/>
+      <c r="V19" s="32"/>
+      <c r="W19" s="33"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A20" s="31"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="32"/>
+      <c r="O20" s="32"/>
+      <c r="P20" s="32"/>
+      <c r="Q20" s="32"/>
+      <c r="R20" s="32"/>
+      <c r="S20" s="32"/>
+      <c r="T20" s="32"/>
+      <c r="U20" s="32"/>
+      <c r="V20" s="32"/>
+      <c r="W20" s="33"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A21" s="31"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32"/>
+      <c r="N21" s="32"/>
+      <c r="O21" s="32"/>
+      <c r="P21" s="32"/>
+      <c r="Q21" s="32"/>
+      <c r="R21" s="32"/>
+      <c r="S21" s="32"/>
+      <c r="T21" s="32"/>
+      <c r="U21" s="32"/>
+      <c r="V21" s="32"/>
+      <c r="W21" s="33"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A22" s="31"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="32"/>
+      <c r="N22" s="32"/>
+      <c r="O22" s="32"/>
+      <c r="P22" s="32"/>
+      <c r="Q22" s="32"/>
+      <c r="R22" s="32"/>
+      <c r="S22" s="32"/>
+      <c r="T22" s="32"/>
+      <c r="U22" s="32"/>
+      <c r="V22" s="32"/>
+      <c r="W22" s="33"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A23" s="31"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32"/>
+      <c r="N23" s="32"/>
+      <c r="O23" s="32"/>
+      <c r="P23" s="32"/>
+      <c r="Q23" s="32"/>
+      <c r="R23" s="32"/>
+      <c r="S23" s="32"/>
+      <c r="T23" s="32"/>
+      <c r="U23" s="32"/>
+      <c r="V23" s="32"/>
+      <c r="W23" s="33"/>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A24" s="31"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+      <c r="N24" s="32"/>
+      <c r="O24" s="32"/>
+      <c r="P24" s="32"/>
+      <c r="Q24" s="32"/>
+      <c r="R24" s="32"/>
+      <c r="S24" s="32"/>
+      <c r="T24" s="32"/>
+      <c r="U24" s="32"/>
+      <c r="V24" s="32"/>
+      <c r="W24" s="33"/>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A25" s="31"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+      <c r="N25" s="32"/>
+      <c r="O25" s="32"/>
+      <c r="P25" s="32"/>
+      <c r="Q25" s="32"/>
+      <c r="R25" s="32"/>
+      <c r="S25" s="32"/>
+      <c r="T25" s="32"/>
+      <c r="U25" s="32"/>
+      <c r="V25" s="32"/>
+      <c r="W25" s="33"/>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A26" s="31"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
+      <c r="N26" s="32"/>
+      <c r="O26" s="32"/>
+      <c r="P26" s="32"/>
+      <c r="Q26" s="32"/>
+      <c r="R26" s="32"/>
+      <c r="S26" s="32"/>
+      <c r="T26" s="32"/>
+      <c r="U26" s="32"/>
+      <c r="V26" s="32"/>
+      <c r="W26" s="33"/>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A27" s="31"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
+      <c r="L27" s="32"/>
+      <c r="M27" s="32"/>
+      <c r="N27" s="32"/>
+      <c r="O27" s="32"/>
+      <c r="P27" s="32"/>
+      <c r="Q27" s="32"/>
+      <c r="R27" s="32"/>
+      <c r="S27" s="32"/>
+      <c r="T27" s="32"/>
+      <c r="U27" s="32"/>
+      <c r="V27" s="32"/>
+      <c r="W27" s="33"/>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A28" s="31"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
+      <c r="T28" s="32"/>
+      <c r="U28" s="32"/>
+      <c r="V28" s="32"/>
+      <c r="W28" s="33"/>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A29" s="31"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
+      <c r="L29" s="32"/>
+      <c r="M29" s="32"/>
+      <c r="N29" s="32"/>
+      <c r="O29" s="32"/>
+      <c r="P29" s="32"/>
+      <c r="Q29" s="32"/>
+      <c r="R29" s="32"/>
+      <c r="S29" s="32"/>
+      <c r="T29" s="32"/>
+      <c r="U29" s="32"/>
+      <c r="V29" s="32"/>
+      <c r="W29" s="33"/>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A30" s="31"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="32"/>
+      <c r="J30" s="32"/>
+      <c r="K30" s="32"/>
+      <c r="L30" s="32"/>
+      <c r="M30" s="32"/>
+      <c r="N30" s="32"/>
+      <c r="O30" s="32"/>
+      <c r="P30" s="32"/>
+      <c r="Q30" s="32"/>
+      <c r="R30" s="32"/>
+      <c r="S30" s="32"/>
+      <c r="T30" s="32"/>
+      <c r="U30" s="32"/>
+      <c r="V30" s="32"/>
+      <c r="W30" s="33"/>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A31" s="31"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
+      <c r="J31" s="32"/>
+      <c r="K31" s="32"/>
+      <c r="L31" s="32"/>
+      <c r="M31" s="32"/>
+      <c r="N31" s="32"/>
+      <c r="O31" s="32"/>
+      <c r="P31" s="32"/>
+      <c r="Q31" s="32"/>
+      <c r="R31" s="32"/>
+      <c r="S31" s="32"/>
+      <c r="T31" s="32"/>
+      <c r="U31" s="32"/>
+      <c r="V31" s="32"/>
+      <c r="W31" s="33"/>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A32" s="31"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
+      <c r="L32" s="32"/>
+      <c r="M32" s="32"/>
+      <c r="N32" s="32"/>
+      <c r="O32" s="32"/>
+      <c r="P32" s="32"/>
+      <c r="Q32" s="32"/>
+      <c r="R32" s="32"/>
+      <c r="S32" s="32"/>
+      <c r="T32" s="32"/>
+      <c r="U32" s="32"/>
+      <c r="V32" s="32"/>
+      <c r="W32" s="33"/>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A33" s="31"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="32"/>
+      <c r="L33" s="32"/>
+      <c r="M33" s="32"/>
+      <c r="N33" s="32"/>
+      <c r="O33" s="32"/>
+      <c r="P33" s="32"/>
+      <c r="Q33" s="32"/>
+      <c r="R33" s="32"/>
+      <c r="S33" s="32"/>
+      <c r="T33" s="32"/>
+      <c r="U33" s="32"/>
+      <c r="V33" s="32"/>
+      <c r="W33" s="33"/>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A34" s="31"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="32"/>
+      <c r="J34" s="32"/>
+      <c r="K34" s="32"/>
+      <c r="L34" s="32"/>
+      <c r="M34" s="32"/>
+      <c r="N34" s="32"/>
+      <c r="O34" s="32"/>
+      <c r="P34" s="32"/>
+      <c r="Q34" s="32"/>
+      <c r="R34" s="32"/>
+      <c r="S34" s="32"/>
+      <c r="T34" s="32"/>
+      <c r="U34" s="32"/>
+      <c r="V34" s="32"/>
+      <c r="W34" s="33"/>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A35" s="31"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
+      <c r="J35" s="32"/>
+      <c r="K35" s="32"/>
+      <c r="L35" s="32"/>
+      <c r="M35" s="32"/>
+      <c r="N35" s="32"/>
+      <c r="O35" s="32"/>
+      <c r="P35" s="32"/>
+      <c r="Q35" s="32"/>
+      <c r="R35" s="32"/>
+      <c r="S35" s="32"/>
+      <c r="T35" s="32"/>
+      <c r="U35" s="32"/>
+      <c r="V35" s="32"/>
+      <c r="W35" s="33"/>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A36" s="31"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="32"/>
+      <c r="N36" s="32"/>
+      <c r="O36" s="32"/>
+      <c r="P36" s="32"/>
+      <c r="Q36" s="32"/>
+      <c r="R36" s="32"/>
+      <c r="S36" s="32"/>
+      <c r="T36" s="32"/>
+      <c r="U36" s="32"/>
+      <c r="V36" s="32"/>
+      <c r="W36" s="33"/>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A37" s="31"/>
+      <c r="B37" s="32"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+      <c r="J37" s="32"/>
+      <c r="K37" s="32"/>
+      <c r="L37" s="32"/>
+      <c r="M37" s="32"/>
+      <c r="N37" s="32"/>
+      <c r="O37" s="32"/>
+      <c r="P37" s="32"/>
+      <c r="Q37" s="32"/>
+      <c r="R37" s="32"/>
+      <c r="S37" s="32"/>
+      <c r="T37" s="32"/>
+      <c r="U37" s="32"/>
+      <c r="V37" s="32"/>
+      <c r="W37" s="33"/>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A38" s="31"/>
+      <c r="B38" s="32"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="32"/>
+      <c r="J38" s="32"/>
+      <c r="K38" s="32"/>
+      <c r="L38" s="32"/>
+      <c r="M38" s="32"/>
+      <c r="N38" s="32"/>
+      <c r="O38" s="32"/>
+      <c r="P38" s="32"/>
+      <c r="Q38" s="32"/>
+      <c r="R38" s="32"/>
+      <c r="S38" s="32"/>
+      <c r="T38" s="32"/>
+      <c r="U38" s="32"/>
+      <c r="V38" s="32"/>
+      <c r="W38" s="33"/>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A39" s="31"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="32"/>
+      <c r="J39" s="32"/>
+      <c r="K39" s="32"/>
+      <c r="L39" s="32"/>
+      <c r="M39" s="32"/>
+      <c r="N39" s="32"/>
+      <c r="O39" s="32"/>
+      <c r="P39" s="32"/>
+      <c r="Q39" s="32"/>
+      <c r="R39" s="32"/>
+      <c r="S39" s="32"/>
+      <c r="T39" s="32"/>
+      <c r="U39" s="32"/>
+      <c r="V39" s="32"/>
+      <c r="W39" s="33"/>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A40" s="31"/>
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="32"/>
+      <c r="J40" s="32"/>
+      <c r="K40" s="32"/>
+      <c r="L40" s="32"/>
+      <c r="M40" s="32"/>
+      <c r="N40" s="32"/>
+      <c r="O40" s="32"/>
+      <c r="P40" s="32"/>
+      <c r="Q40" s="32"/>
+      <c r="R40" s="32"/>
+      <c r="S40" s="32"/>
+      <c r="T40" s="32"/>
+      <c r="U40" s="32"/>
+      <c r="V40" s="32"/>
+      <c r="W40" s="33"/>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A41" s="31"/>
+      <c r="B41" s="32"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="32"/>
+      <c r="J41" s="32"/>
+      <c r="K41" s="32"/>
+      <c r="L41" s="32"/>
+      <c r="M41" s="32"/>
+      <c r="N41" s="32"/>
+      <c r="O41" s="32"/>
+      <c r="P41" s="32"/>
+      <c r="Q41" s="32"/>
+      <c r="R41" s="32"/>
+      <c r="S41" s="32"/>
+      <c r="T41" s="32"/>
+      <c r="U41" s="32"/>
+      <c r="V41" s="32"/>
+      <c r="W41" s="33"/>
+      <c r="X41" s="16" t="s">
         <v>760</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="24" t="s">
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A42" s="31"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="32"/>
+      <c r="M42" s="32"/>
+      <c r="N42" s="32"/>
+      <c r="O42" s="32"/>
+      <c r="P42" s="32"/>
+      <c r="Q42" s="32"/>
+      <c r="R42" s="32"/>
+      <c r="S42" s="32"/>
+      <c r="T42" s="32"/>
+      <c r="U42" s="32"/>
+      <c r="V42" s="32"/>
+      <c r="W42" s="33"/>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A43" s="31"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="32"/>
+      <c r="J43" s="32"/>
+      <c r="K43" s="32"/>
+      <c r="L43" s="32"/>
+      <c r="M43" s="32"/>
+      <c r="N43" s="32"/>
+      <c r="O43" s="32"/>
+      <c r="P43" s="32"/>
+      <c r="Q43" s="32"/>
+      <c r="R43" s="32"/>
+      <c r="S43" s="32"/>
+      <c r="T43" s="32"/>
+      <c r="U43" s="32"/>
+      <c r="V43" s="32"/>
+      <c r="W43" s="33"/>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A44" s="31"/>
+      <c r="B44" s="32"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="32"/>
+      <c r="I44" s="32"/>
+      <c r="J44" s="32"/>
+      <c r="K44" s="32"/>
+      <c r="L44" s="32"/>
+      <c r="M44" s="32"/>
+      <c r="N44" s="32"/>
+      <c r="O44" s="32"/>
+      <c r="P44" s="32"/>
+      <c r="Q44" s="32"/>
+      <c r="R44" s="32"/>
+      <c r="S44" s="32"/>
+      <c r="T44" s="32"/>
+      <c r="U44" s="32"/>
+      <c r="V44" s="32"/>
+      <c r="W44" s="33"/>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A45" s="31"/>
+      <c r="B45" s="32"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="32"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="32"/>
+      <c r="J45" s="32"/>
+      <c r="K45" s="32"/>
+      <c r="L45" s="32"/>
+      <c r="M45" s="32"/>
+      <c r="N45" s="32"/>
+      <c r="O45" s="32"/>
+      <c r="P45" s="32"/>
+      <c r="Q45" s="32"/>
+      <c r="R45" s="32"/>
+      <c r="S45" s="32"/>
+      <c r="T45" s="32"/>
+      <c r="U45" s="32"/>
+      <c r="V45" s="32"/>
+      <c r="W45" s="33"/>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A46" s="31"/>
+      <c r="B46" s="32"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
+      <c r="J46" s="32"/>
+      <c r="K46" s="32"/>
+      <c r="L46" s="32"/>
+      <c r="M46" s="32"/>
+      <c r="N46" s="32"/>
+      <c r="O46" s="32"/>
+      <c r="P46" s="32"/>
+      <c r="Q46" s="32"/>
+      <c r="R46" s="32"/>
+      <c r="S46" s="32"/>
+      <c r="T46" s="32"/>
+      <c r="U46" s="32"/>
+      <c r="V46" s="32"/>
+      <c r="W46" s="33"/>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A47" s="31"/>
+      <c r="B47" s="32"/>
+      <c r="C47" s="32"/>
+      <c r="D47" s="32"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="32"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="32"/>
+      <c r="I47" s="32"/>
+      <c r="J47" s="32"/>
+      <c r="K47" s="32"/>
+      <c r="L47" s="32"/>
+      <c r="M47" s="32"/>
+      <c r="N47" s="32"/>
+      <c r="O47" s="32"/>
+      <c r="P47" s="32"/>
+      <c r="Q47" s="32"/>
+      <c r="R47" s="32"/>
+      <c r="S47" s="32"/>
+      <c r="T47" s="32"/>
+      <c r="U47" s="32"/>
+      <c r="V47" s="32"/>
+      <c r="W47" s="33"/>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A48" s="31"/>
+      <c r="B48" s="32"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="32"/>
+      <c r="F48" s="32"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="32"/>
+      <c r="I48" s="32"/>
+      <c r="J48" s="32"/>
+      <c r="K48" s="32"/>
+      <c r="L48" s="32"/>
+      <c r="M48" s="32"/>
+      <c r="N48" s="32"/>
+      <c r="O48" s="32"/>
+      <c r="P48" s="32"/>
+      <c r="Q48" s="32"/>
+      <c r="R48" s="32"/>
+      <c r="S48" s="32"/>
+      <c r="T48" s="32"/>
+      <c r="U48" s="32"/>
+      <c r="V48" s="32"/>
+      <c r="W48" s="33"/>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A49" s="31"/>
+      <c r="B49" s="32"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
+      <c r="J49" s="32"/>
+      <c r="K49" s="32"/>
+      <c r="L49" s="32"/>
+      <c r="M49" s="32"/>
+      <c r="N49" s="32"/>
+      <c r="O49" s="32"/>
+      <c r="P49" s="32"/>
+      <c r="Q49" s="32"/>
+      <c r="R49" s="32"/>
+      <c r="S49" s="32"/>
+      <c r="T49" s="32"/>
+      <c r="U49" s="32"/>
+      <c r="V49" s="32"/>
+      <c r="W49" s="33"/>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A50" s="31"/>
+      <c r="B50" s="32"/>
+      <c r="C50" s="32"/>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="32"/>
+      <c r="J50" s="32"/>
+      <c r="K50" s="32"/>
+      <c r="L50" s="32"/>
+      <c r="M50" s="32"/>
+      <c r="N50" s="32"/>
+      <c r="O50" s="32"/>
+      <c r="P50" s="32"/>
+      <c r="Q50" s="32"/>
+      <c r="R50" s="32"/>
+      <c r="S50" s="32"/>
+      <c r="T50" s="32"/>
+      <c r="U50" s="32"/>
+      <c r="V50" s="32"/>
+      <c r="W50" s="33"/>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A51" s="31"/>
+      <c r="B51" s="32"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="32"/>
+      <c r="I51" s="32"/>
+      <c r="J51" s="32"/>
+      <c r="K51" s="32"/>
+      <c r="L51" s="32"/>
+      <c r="M51" s="32"/>
+      <c r="N51" s="32"/>
+      <c r="O51" s="32"/>
+      <c r="P51" s="32"/>
+      <c r="Q51" s="32"/>
+      <c r="R51" s="32"/>
+      <c r="S51" s="32"/>
+      <c r="T51" s="32"/>
+      <c r="U51" s="32"/>
+      <c r="V51" s="32"/>
+      <c r="W51" s="33"/>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A52" s="31"/>
+      <c r="B52" s="32"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="32"/>
+      <c r="I52" s="32"/>
+      <c r="J52" s="32"/>
+      <c r="K52" s="32"/>
+      <c r="L52" s="32"/>
+      <c r="M52" s="32"/>
+      <c r="N52" s="32"/>
+      <c r="O52" s="32"/>
+      <c r="P52" s="32"/>
+      <c r="Q52" s="32"/>
+      <c r="R52" s="32"/>
+      <c r="S52" s="32"/>
+      <c r="T52" s="32"/>
+      <c r="U52" s="32"/>
+      <c r="V52" s="32"/>
+      <c r="W52" s="33"/>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A53" s="31"/>
+      <c r="B53" s="32"/>
+      <c r="C53" s="32"/>
+      <c r="D53" s="32"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="32"/>
+      <c r="I53" s="32"/>
+      <c r="J53" s="32"/>
+      <c r="K53" s="32"/>
+      <c r="L53" s="32"/>
+      <c r="M53" s="32"/>
+      <c r="N53" s="32"/>
+      <c r="O53" s="32"/>
+      <c r="P53" s="32"/>
+      <c r="Q53" s="32"/>
+      <c r="R53" s="32"/>
+      <c r="S53" s="32"/>
+      <c r="T53" s="32"/>
+      <c r="U53" s="32"/>
+      <c r="V53" s="32"/>
+      <c r="W53" s="33"/>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A54" s="31"/>
+      <c r="B54" s="32"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="32"/>
+      <c r="E54" s="32"/>
+      <c r="F54" s="32"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="32"/>
+      <c r="I54" s="32"/>
+      <c r="J54" s="32"/>
+      <c r="K54" s="32"/>
+      <c r="L54" s="32"/>
+      <c r="M54" s="32"/>
+      <c r="N54" s="32"/>
+      <c r="O54" s="32"/>
+      <c r="P54" s="32"/>
+      <c r="Q54" s="32"/>
+      <c r="R54" s="32"/>
+      <c r="S54" s="32"/>
+      <c r="T54" s="32"/>
+      <c r="U54" s="32"/>
+      <c r="V54" s="32"/>
+      <c r="W54" s="33"/>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A55" s="31"/>
+      <c r="B55" s="32"/>
+      <c r="C55" s="32"/>
+      <c r="D55" s="32"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="32"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32"/>
+      <c r="I55" s="32"/>
+      <c r="J55" s="32"/>
+      <c r="K55" s="32"/>
+      <c r="L55" s="32"/>
+      <c r="M55" s="32"/>
+      <c r="N55" s="32"/>
+      <c r="O55" s="32"/>
+      <c r="P55" s="32"/>
+      <c r="Q55" s="32"/>
+      <c r="R55" s="32"/>
+      <c r="S55" s="32"/>
+      <c r="T55" s="32"/>
+      <c r="U55" s="32"/>
+      <c r="V55" s="32"/>
+      <c r="W55" s="33"/>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A56" s="31"/>
+      <c r="B56" s="32"/>
+      <c r="C56" s="32"/>
+      <c r="D56" s="32"/>
+      <c r="E56" s="32"/>
+      <c r="F56" s="32"/>
+      <c r="G56" s="32"/>
+      <c r="H56" s="32"/>
+      <c r="I56" s="32"/>
+      <c r="J56" s="32"/>
+      <c r="K56" s="32"/>
+      <c r="L56" s="32"/>
+      <c r="M56" s="32"/>
+      <c r="N56" s="32"/>
+      <c r="O56" s="32"/>
+      <c r="P56" s="32"/>
+      <c r="Q56" s="32"/>
+      <c r="R56" s="32"/>
+      <c r="S56" s="32"/>
+      <c r="T56" s="32"/>
+      <c r="U56" s="32"/>
+      <c r="V56" s="32"/>
+      <c r="W56" s="33"/>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A57" s="31"/>
+      <c r="B57" s="32"/>
+      <c r="C57" s="32"/>
+      <c r="D57" s="32"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="32"/>
+      <c r="H57" s="32"/>
+      <c r="I57" s="32"/>
+      <c r="J57" s="32"/>
+      <c r="K57" s="32"/>
+      <c r="L57" s="32"/>
+      <c r="M57" s="32"/>
+      <c r="N57" s="32"/>
+      <c r="O57" s="32"/>
+      <c r="P57" s="32"/>
+      <c r="Q57" s="32"/>
+      <c r="R57" s="32"/>
+      <c r="S57" s="32"/>
+      <c r="T57" s="32"/>
+      <c r="U57" s="32"/>
+      <c r="V57" s="32"/>
+      <c r="W57" s="33"/>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A58" s="31"/>
+      <c r="B58" s="32"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="32"/>
+      <c r="I58" s="32"/>
+      <c r="J58" s="32"/>
+      <c r="K58" s="32"/>
+      <c r="L58" s="32"/>
+      <c r="M58" s="32"/>
+      <c r="N58" s="32"/>
+      <c r="O58" s="32"/>
+      <c r="P58" s="32"/>
+      <c r="Q58" s="32"/>
+      <c r="R58" s="32"/>
+      <c r="S58" s="32"/>
+      <c r="T58" s="32"/>
+      <c r="U58" s="32"/>
+      <c r="V58" s="32"/>
+      <c r="W58" s="33"/>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A59" s="31"/>
+      <c r="B59" s="32"/>
+      <c r="C59" s="32"/>
+      <c r="D59" s="32"/>
+      <c r="E59" s="32"/>
+      <c r="F59" s="32"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="32"/>
+      <c r="I59" s="32"/>
+      <c r="J59" s="32"/>
+      <c r="K59" s="32"/>
+      <c r="L59" s="32"/>
+      <c r="M59" s="32"/>
+      <c r="N59" s="32"/>
+      <c r="O59" s="32"/>
+      <c r="P59" s="32"/>
+      <c r="Q59" s="32"/>
+      <c r="R59" s="32"/>
+      <c r="S59" s="32"/>
+      <c r="T59" s="32"/>
+      <c r="U59" s="32"/>
+      <c r="V59" s="32"/>
+      <c r="W59" s="33"/>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A60" s="31"/>
+      <c r="B60" s="32"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="32"/>
+      <c r="E60" s="32"/>
+      <c r="F60" s="32"/>
+      <c r="G60" s="32"/>
+      <c r="H60" s="32"/>
+      <c r="I60" s="32"/>
+      <c r="J60" s="32"/>
+      <c r="K60" s="32"/>
+      <c r="L60" s="32"/>
+      <c r="M60" s="32"/>
+      <c r="N60" s="32"/>
+      <c r="O60" s="32"/>
+      <c r="P60" s="32"/>
+      <c r="Q60" s="32"/>
+      <c r="R60" s="32"/>
+      <c r="S60" s="32"/>
+      <c r="T60" s="32"/>
+      <c r="U60" s="32"/>
+      <c r="V60" s="32"/>
+      <c r="W60" s="33"/>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A61" s="31"/>
+      <c r="B61" s="32"/>
+      <c r="C61" s="32"/>
+      <c r="D61" s="32"/>
+      <c r="E61" s="32"/>
+      <c r="F61" s="32"/>
+      <c r="G61" s="32"/>
+      <c r="H61" s="32"/>
+      <c r="I61" s="32"/>
+      <c r="J61" s="32"/>
+      <c r="K61" s="32"/>
+      <c r="L61" s="32"/>
+      <c r="M61" s="32"/>
+      <c r="N61" s="32"/>
+      <c r="O61" s="32"/>
+      <c r="P61" s="32"/>
+      <c r="Q61" s="32"/>
+      <c r="R61" s="32"/>
+      <c r="S61" s="32"/>
+      <c r="T61" s="32"/>
+      <c r="U61" s="32"/>
+      <c r="V61" s="32"/>
+      <c r="W61" s="33"/>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A62" s="31"/>
+      <c r="B62" s="32"/>
+      <c r="C62" s="32"/>
+      <c r="D62" s="32"/>
+      <c r="E62" s="32"/>
+      <c r="F62" s="32"/>
+      <c r="G62" s="32"/>
+      <c r="H62" s="32"/>
+      <c r="I62" s="32"/>
+      <c r="J62" s="32"/>
+      <c r="K62" s="32"/>
+      <c r="L62" s="32"/>
+      <c r="M62" s="32"/>
+      <c r="N62" s="32"/>
+      <c r="O62" s="32"/>
+      <c r="P62" s="32"/>
+      <c r="Q62" s="32"/>
+      <c r="R62" s="32"/>
+      <c r="S62" s="32"/>
+      <c r="T62" s="32"/>
+      <c r="U62" s="32"/>
+      <c r="V62" s="32"/>
+      <c r="W62" s="33"/>
+    </row>
+    <row r="63" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="34"/>
+      <c r="B63" s="35"/>
+      <c r="C63" s="35"/>
+      <c r="D63" s="35"/>
+      <c r="E63" s="35"/>
+      <c r="F63" s="35"/>
+      <c r="G63" s="35"/>
+      <c r="H63" s="35"/>
+      <c r="I63" s="35"/>
+      <c r="J63" s="35"/>
+      <c r="K63" s="35"/>
+      <c r="L63" s="35"/>
+      <c r="M63" s="35"/>
+      <c r="N63" s="35"/>
+      <c r="O63" s="35"/>
+      <c r="P63" s="35"/>
+      <c r="Q63" s="35"/>
+      <c r="R63" s="35"/>
+      <c r="S63" s="35"/>
+      <c r="T63" s="35"/>
+      <c r="U63" s="35"/>
+      <c r="V63" s="35"/>
+      <c r="W63" s="36"/>
+    </row>
+    <row r="64" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="37"/>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A65" s="38" t="s">
+        <v>764</v>
+      </c>
+      <c r="B65" s="39"/>
+      <c r="C65" s="39"/>
+      <c r="D65" s="39"/>
+      <c r="E65" s="39"/>
+      <c r="F65" s="39"/>
+      <c r="G65" s="39"/>
+      <c r="H65" s="39"/>
+      <c r="I65" s="39"/>
+      <c r="J65" s="39"/>
+      <c r="K65" s="39"/>
+      <c r="L65" s="39"/>
+      <c r="M65" s="39"/>
+      <c r="N65" s="39"/>
+      <c r="O65" s="39"/>
+      <c r="P65" s="39"/>
+      <c r="Q65" s="39"/>
+      <c r="R65" s="39"/>
+      <c r="S65" s="39"/>
+      <c r="T65" s="39"/>
+      <c r="U65" s="39"/>
+      <c r="V65" s="39"/>
+      <c r="W65" s="40"/>
+    </row>
+    <row r="66" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="41"/>
+      <c r="B66" s="42"/>
+      <c r="C66" s="42"/>
+      <c r="D66" s="42"/>
+      <c r="E66" s="42"/>
+      <c r="F66" s="42"/>
+      <c r="G66" s="42"/>
+      <c r="H66" s="42"/>
+      <c r="I66" s="42"/>
+      <c r="J66" s="42"/>
+      <c r="K66" s="42"/>
+      <c r="L66" s="42"/>
+      <c r="M66" s="42"/>
+      <c r="N66" s="42"/>
+      <c r="O66" s="42"/>
+      <c r="P66" s="42"/>
+      <c r="Q66" s="42"/>
+      <c r="R66" s="42"/>
+      <c r="S66" s="42"/>
+      <c r="T66" s="42"/>
+      <c r="U66" s="42"/>
+      <c r="V66" s="42"/>
+      <c r="W66" s="43"/>
+    </row>
+    <row r="67" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="44" t="s">
         <v>761</v>
       </c>
-      <c r="M17" s="25"/>
-      <c r="N17" s="25"/>
-      <c r="O17" s="25"/>
-      <c r="P17" s="25"/>
-      <c r="Q17" s="25"/>
-      <c r="R17" s="25"/>
-      <c r="S17" s="25"/>
-      <c r="T17" s="25"/>
-      <c r="U17" s="25"/>
-      <c r="V17" s="25"/>
-      <c r="W17" s="26"/>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A18" s="27"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
-      <c r="K18" s="29"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="31"/>
-      <c r="N18" s="31"/>
-      <c r="O18" s="31"/>
-      <c r="P18" s="31"/>
-      <c r="Q18" s="31"/>
-      <c r="R18" s="31"/>
-      <c r="S18" s="31"/>
-      <c r="T18" s="31"/>
-      <c r="U18" s="31"/>
-      <c r="V18" s="31"/>
-      <c r="W18" s="32"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A19" s="27"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="29"/>
-      <c r="L19" s="30"/>
-      <c r="M19" s="31"/>
-      <c r="N19" s="31"/>
-      <c r="O19" s="31"/>
-      <c r="P19" s="31"/>
-      <c r="Q19" s="31"/>
-      <c r="R19" s="31"/>
-      <c r="S19" s="31"/>
-      <c r="T19" s="31"/>
-      <c r="U19" s="31"/>
-      <c r="V19" s="31"/>
-      <c r="W19" s="32"/>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A20" s="27"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="31"/>
-      <c r="N20" s="31"/>
-      <c r="O20" s="31"/>
-      <c r="P20" s="31"/>
-      <c r="Q20" s="31"/>
-      <c r="R20" s="31"/>
-      <c r="S20" s="31"/>
-      <c r="T20" s="31"/>
-      <c r="U20" s="31"/>
-      <c r="V20" s="31"/>
-      <c r="W20" s="32"/>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A21" s="27"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="28"/>
-      <c r="K21" s="29"/>
-      <c r="L21" s="30"/>
-      <c r="M21" s="31"/>
-      <c r="N21" s="31"/>
-      <c r="O21" s="31"/>
-      <c r="P21" s="31"/>
-      <c r="Q21" s="31"/>
-      <c r="R21" s="31"/>
-      <c r="S21" s="31"/>
-      <c r="T21" s="31"/>
-      <c r="U21" s="31"/>
-      <c r="V21" s="31"/>
-      <c r="W21" s="32"/>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A22" s="27"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="28"/>
-      <c r="K22" s="29"/>
-      <c r="L22" s="30"/>
-      <c r="M22" s="31"/>
-      <c r="N22" s="31"/>
-      <c r="O22" s="31"/>
-      <c r="P22" s="31"/>
-      <c r="Q22" s="31"/>
-      <c r="R22" s="31"/>
-      <c r="S22" s="31"/>
-      <c r="T22" s="31"/>
-      <c r="U22" s="31"/>
-      <c r="V22" s="31"/>
-      <c r="W22" s="32"/>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A23" s="27"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="31"/>
-      <c r="N23" s="31"/>
-      <c r="O23" s="31"/>
-      <c r="P23" s="31"/>
-      <c r="Q23" s="31"/>
-      <c r="R23" s="31"/>
-      <c r="S23" s="31"/>
-      <c r="T23" s="31"/>
-      <c r="U23" s="31"/>
-      <c r="V23" s="31"/>
-      <c r="W23" s="32"/>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A24" s="27"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28"/>
-      <c r="K24" s="29"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="31"/>
-      <c r="N24" s="31"/>
-      <c r="O24" s="31"/>
-      <c r="P24" s="31"/>
-      <c r="Q24" s="31"/>
-      <c r="R24" s="31"/>
-      <c r="S24" s="31"/>
-      <c r="T24" s="31"/>
-      <c r="U24" s="31"/>
-      <c r="V24" s="31"/>
-      <c r="W24" s="32"/>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A25" s="27"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28"/>
-      <c r="K25" s="29"/>
-      <c r="L25" s="30"/>
-      <c r="M25" s="31"/>
-      <c r="N25" s="31"/>
-      <c r="O25" s="31"/>
-      <c r="P25" s="31"/>
-      <c r="Q25" s="31"/>
-      <c r="R25" s="31"/>
-      <c r="S25" s="31"/>
-      <c r="T25" s="31"/>
-      <c r="U25" s="31"/>
-      <c r="V25" s="31"/>
-      <c r="W25" s="32"/>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A26" s="27"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="30"/>
-      <c r="M26" s="31"/>
-      <c r="N26" s="31"/>
-      <c r="O26" s="31"/>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
-      <c r="S26" s="31"/>
-      <c r="T26" s="31"/>
-      <c r="U26" s="31"/>
-      <c r="V26" s="31"/>
-      <c r="W26" s="32"/>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A27" s="27"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="28"/>
-      <c r="K27" s="29"/>
-      <c r="L27" s="30"/>
-      <c r="M27" s="31"/>
-      <c r="N27" s="31"/>
-      <c r="O27" s="31"/>
-      <c r="P27" s="31"/>
-      <c r="Q27" s="31"/>
-      <c r="R27" s="31"/>
-      <c r="S27" s="31"/>
-      <c r="T27" s="31"/>
-      <c r="U27" s="31"/>
-      <c r="V27" s="31"/>
-      <c r="W27" s="32"/>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A28" s="27"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="28"/>
-      <c r="K28" s="29"/>
-      <c r="L28" s="30"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
-      <c r="T28" s="31"/>
-      <c r="U28" s="31"/>
-      <c r="V28" s="31"/>
-      <c r="W28" s="32"/>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A29" s="27"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="28"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="31"/>
-      <c r="N29" s="31"/>
-      <c r="O29" s="31"/>
-      <c r="P29" s="31"/>
-      <c r="Q29" s="31"/>
-      <c r="R29" s="31"/>
-      <c r="S29" s="31"/>
-      <c r="T29" s="31"/>
-      <c r="U29" s="31"/>
-      <c r="V29" s="31"/>
-      <c r="W29" s="32"/>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A30" s="27"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
-      <c r="J30" s="28"/>
-      <c r="K30" s="29"/>
-      <c r="L30" s="30"/>
-      <c r="M30" s="31"/>
-      <c r="N30" s="31"/>
-      <c r="O30" s="31"/>
-      <c r="P30" s="31"/>
-      <c r="Q30" s="31"/>
-      <c r="R30" s="31"/>
-      <c r="S30" s="31"/>
-      <c r="T30" s="31"/>
-      <c r="U30" s="31"/>
-      <c r="V30" s="31"/>
-      <c r="W30" s="32"/>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A31" s="27"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="28"/>
-      <c r="J31" s="28"/>
-      <c r="K31" s="29"/>
-      <c r="L31" s="30"/>
-      <c r="M31" s="31"/>
-      <c r="N31" s="31"/>
-      <c r="O31" s="31"/>
-      <c r="P31" s="31"/>
-      <c r="Q31" s="31"/>
-      <c r="R31" s="31"/>
-      <c r="S31" s="31"/>
-      <c r="T31" s="31"/>
-      <c r="U31" s="31"/>
-      <c r="V31" s="31"/>
-      <c r="W31" s="32"/>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A32" s="27"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="31"/>
-      <c r="N32" s="31"/>
-      <c r="O32" s="31"/>
-      <c r="P32" s="31"/>
-      <c r="Q32" s="31"/>
-      <c r="R32" s="31"/>
-      <c r="S32" s="31"/>
-      <c r="T32" s="31"/>
-      <c r="U32" s="31"/>
-      <c r="V32" s="31"/>
-      <c r="W32" s="32"/>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A33" s="27"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="28"/>
-      <c r="K33" s="29"/>
-      <c r="L33" s="30"/>
-      <c r="M33" s="31"/>
-      <c r="N33" s="31"/>
-      <c r="O33" s="31"/>
-      <c r="P33" s="31"/>
-      <c r="Q33" s="31"/>
-      <c r="R33" s="31"/>
-      <c r="S33" s="31"/>
-      <c r="T33" s="31"/>
-      <c r="U33" s="31"/>
-      <c r="V33" s="31"/>
-      <c r="W33" s="32"/>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A34" s="27"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="28"/>
-      <c r="K34" s="29"/>
-      <c r="L34" s="30"/>
-      <c r="M34" s="31"/>
-      <c r="N34" s="31"/>
-      <c r="O34" s="31"/>
-      <c r="P34" s="31"/>
-      <c r="Q34" s="31"/>
-      <c r="R34" s="31"/>
-      <c r="S34" s="31"/>
-      <c r="T34" s="31"/>
-      <c r="U34" s="31"/>
-      <c r="V34" s="31"/>
-      <c r="W34" s="32"/>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A35" s="27"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="28"/>
-      <c r="J35" s="28"/>
-      <c r="K35" s="29"/>
-      <c r="L35" s="30"/>
-      <c r="M35" s="31"/>
-      <c r="N35" s="31"/>
-      <c r="O35" s="31"/>
-      <c r="P35" s="31"/>
-      <c r="Q35" s="31"/>
-      <c r="R35" s="31"/>
-      <c r="S35" s="31"/>
-      <c r="T35" s="31"/>
-      <c r="U35" s="31"/>
-      <c r="V35" s="31"/>
-      <c r="W35" s="32"/>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A36" s="27"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28"/>
-      <c r="J36" s="28"/>
-      <c r="K36" s="29"/>
-      <c r="L36" s="30"/>
-      <c r="M36" s="31"/>
-      <c r="N36" s="31"/>
-      <c r="O36" s="31"/>
-      <c r="P36" s="31"/>
-      <c r="Q36" s="31"/>
-      <c r="R36" s="31"/>
-      <c r="S36" s="31"/>
-      <c r="T36" s="31"/>
-      <c r="U36" s="31"/>
-      <c r="V36" s="31"/>
-      <c r="W36" s="32"/>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A37" s="27"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="28"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="31"/>
-      <c r="N37" s="31"/>
-      <c r="O37" s="31"/>
-      <c r="P37" s="31"/>
-      <c r="Q37" s="31"/>
-      <c r="R37" s="31"/>
-      <c r="S37" s="31"/>
-      <c r="T37" s="31"/>
-      <c r="U37" s="31"/>
-      <c r="V37" s="31"/>
-      <c r="W37" s="32"/>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A38" s="27"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="28"/>
-      <c r="K38" s="29"/>
-      <c r="L38" s="30"/>
-      <c r="M38" s="31"/>
-      <c r="N38" s="31"/>
-      <c r="O38" s="31"/>
-      <c r="P38" s="31"/>
-      <c r="Q38" s="31"/>
-      <c r="R38" s="31"/>
-      <c r="S38" s="31"/>
-      <c r="T38" s="31"/>
-      <c r="U38" s="31"/>
-      <c r="V38" s="31"/>
-      <c r="W38" s="32"/>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A39" s="27"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="28"/>
-      <c r="J39" s="28"/>
-      <c r="K39" s="29"/>
-      <c r="L39" s="30"/>
-      <c r="M39" s="31"/>
-      <c r="N39" s="31"/>
-      <c r="O39" s="31"/>
-      <c r="P39" s="31"/>
-      <c r="Q39" s="31"/>
-      <c r="R39" s="31"/>
-      <c r="S39" s="31"/>
-      <c r="T39" s="31"/>
-      <c r="U39" s="31"/>
-      <c r="V39" s="31"/>
-      <c r="W39" s="32"/>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A40" s="27"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="31"/>
-      <c r="N40" s="31"/>
-      <c r="O40" s="31"/>
-      <c r="P40" s="31"/>
-      <c r="Q40" s="31"/>
-      <c r="R40" s="31"/>
-      <c r="S40" s="31"/>
-      <c r="T40" s="31"/>
-      <c r="U40" s="31"/>
-      <c r="V40" s="31"/>
-      <c r="W40" s="32"/>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A41" s="27"/>
-      <c r="B41" s="28"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="28"/>
-      <c r="J41" s="28"/>
-      <c r="K41" s="29"/>
-      <c r="L41" s="30"/>
-      <c r="M41" s="31"/>
-      <c r="N41" s="31"/>
-      <c r="O41" s="31"/>
-      <c r="P41" s="31"/>
-      <c r="Q41" s="31"/>
-      <c r="R41" s="31"/>
-      <c r="S41" s="31"/>
-      <c r="T41" s="31"/>
-      <c r="U41" s="31"/>
-      <c r="V41" s="31"/>
-      <c r="W41" s="32"/>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A42" s="27"/>
-      <c r="B42" s="28"/>
-      <c r="C42" s="28"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="28"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="28"/>
-      <c r="I42" s="28"/>
-      <c r="J42" s="28"/>
-      <c r="K42" s="29"/>
-      <c r="L42" s="30"/>
-      <c r="M42" s="31"/>
-      <c r="N42" s="31"/>
-      <c r="O42" s="31"/>
-      <c r="P42" s="31"/>
-      <c r="Q42" s="31"/>
-      <c r="R42" s="31"/>
-      <c r="S42" s="31"/>
-      <c r="T42" s="31"/>
-      <c r="U42" s="31"/>
-      <c r="V42" s="31"/>
-      <c r="W42" s="32"/>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A43" s="27"/>
-      <c r="B43" s="28"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28"/>
-      <c r="J43" s="28"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="30"/>
-      <c r="M43" s="31"/>
-      <c r="N43" s="31"/>
-      <c r="O43" s="31"/>
-      <c r="P43" s="31"/>
-      <c r="Q43" s="31"/>
-      <c r="R43" s="31"/>
-      <c r="S43" s="31"/>
-      <c r="T43" s="31"/>
-      <c r="U43" s="31"/>
-      <c r="V43" s="31"/>
-      <c r="W43" s="32"/>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A44" s="27"/>
-      <c r="B44" s="28"/>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="28"/>
-      <c r="J44" s="28"/>
-      <c r="K44" s="29"/>
-      <c r="L44" s="30"/>
-      <c r="M44" s="31"/>
-      <c r="N44" s="31"/>
-      <c r="O44" s="31"/>
-      <c r="P44" s="31"/>
-      <c r="Q44" s="31"/>
-      <c r="R44" s="31"/>
-      <c r="S44" s="31"/>
-      <c r="T44" s="31"/>
-      <c r="U44" s="31"/>
-      <c r="V44" s="31"/>
-      <c r="W44" s="32"/>
-    </row>
-    <row r="45" spans="1:23" ht="63" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="27"/>
-      <c r="B45" s="28"/>
-      <c r="C45" s="28"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="28"/>
-      <c r="J45" s="28"/>
-      <c r="K45" s="29"/>
-      <c r="L45" s="30"/>
-      <c r="M45" s="31"/>
-      <c r="N45" s="31"/>
-      <c r="O45" s="31"/>
-      <c r="P45" s="31"/>
-      <c r="Q45" s="31"/>
-      <c r="R45" s="31"/>
-      <c r="S45" s="31"/>
-      <c r="T45" s="31"/>
-      <c r="U45" s="31"/>
-      <c r="V45" s="31"/>
-      <c r="W45" s="32"/>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A46" s="27"/>
-      <c r="B46" s="28"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="28"/>
-      <c r="J46" s="28"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="31"/>
-      <c r="N46" s="31"/>
-      <c r="O46" s="31"/>
-      <c r="P46" s="31"/>
-      <c r="Q46" s="31"/>
-      <c r="R46" s="31"/>
-      <c r="S46" s="31"/>
-      <c r="T46" s="31"/>
-      <c r="U46" s="31"/>
-      <c r="V46" s="31"/>
-      <c r="W46" s="32"/>
-    </row>
-    <row r="47" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="33"/>
-      <c r="B47" s="34"/>
-      <c r="C47" s="34"/>
-      <c r="D47" s="34"/>
-      <c r="E47" s="34"/>
-      <c r="F47" s="34"/>
-      <c r="G47" s="34"/>
-      <c r="H47" s="34"/>
-      <c r="I47" s="34"/>
-      <c r="J47" s="34"/>
-      <c r="K47" s="35"/>
-      <c r="L47" s="36"/>
-      <c r="M47" s="37"/>
-      <c r="N47" s="37"/>
-      <c r="O47" s="37"/>
-      <c r="P47" s="37"/>
-      <c r="Q47" s="37"/>
-      <c r="R47" s="37"/>
-      <c r="S47" s="37"/>
-      <c r="T47" s="37"/>
-      <c r="U47" s="37"/>
-      <c r="V47" s="37"/>
-      <c r="W47" s="38"/>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A48" s="39" t="s">
-        <v>762</v>
-      </c>
-      <c r="B48" s="40"/>
-      <c r="C48" s="40"/>
-      <c r="D48" s="40"/>
-      <c r="E48" s="40"/>
-      <c r="F48" s="40"/>
-      <c r="G48" s="40"/>
-      <c r="H48" s="40"/>
-      <c r="I48" s="40"/>
-      <c r="J48" s="40"/>
-      <c r="K48" s="40"/>
-      <c r="L48" s="40"/>
-      <c r="M48" s="40"/>
-      <c r="N48" s="40"/>
-      <c r="O48" s="40"/>
-      <c r="P48" s="40"/>
-      <c r="Q48" s="40"/>
-      <c r="R48" s="40"/>
-      <c r="S48" s="40"/>
-      <c r="T48" s="40"/>
-      <c r="U48" s="40"/>
-      <c r="V48" s="40"/>
-      <c r="W48" s="41"/>
-    </row>
-    <row r="49" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="42"/>
-      <c r="B49" s="43"/>
-      <c r="C49" s="43"/>
-      <c r="D49" s="43"/>
-      <c r="E49" s="43"/>
-      <c r="F49" s="43"/>
-      <c r="G49" s="43"/>
-      <c r="H49" s="43"/>
-      <c r="I49" s="43"/>
-      <c r="J49" s="43"/>
-      <c r="K49" s="43"/>
-      <c r="L49" s="43"/>
-      <c r="M49" s="43"/>
-      <c r="N49" s="43"/>
-      <c r="O49" s="43"/>
-      <c r="P49" s="43"/>
-      <c r="Q49" s="43"/>
-      <c r="R49" s="43"/>
-      <c r="S49" s="43"/>
-      <c r="T49" s="43"/>
-      <c r="U49" s="43"/>
-      <c r="V49" s="43"/>
-      <c r="W49" s="44"/>
-    </row>
-    <row r="50" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="45" t="s">
-        <v>763</v>
-      </c>
-      <c r="B50" s="46"/>
-      <c r="C50" s="46"/>
-      <c r="D50" s="46"/>
-      <c r="E50" s="46"/>
-      <c r="F50" s="46"/>
-      <c r="G50" s="46"/>
-      <c r="H50" s="46"/>
-      <c r="I50" s="46"/>
-      <c r="J50" s="46"/>
-      <c r="K50" s="46"/>
-      <c r="L50" s="46"/>
-      <c r="M50" s="46"/>
-      <c r="N50" s="46"/>
-      <c r="O50" s="46"/>
-      <c r="P50" s="46"/>
-      <c r="Q50" s="46"/>
-      <c r="R50" s="46"/>
-      <c r="S50" s="46"/>
-      <c r="T50" s="46"/>
-      <c r="U50" s="46"/>
-      <c r="V50" s="46"/>
-      <c r="W50" s="47"/>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="S51" s="48" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A59" s="49"/>
-    </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A60" s="50"/>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A61" s="50"/>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A62" s="50"/>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A63" s="50"/>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A64" s="50"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="50"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="50"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="50"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="50"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="50"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="50"/>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="50"/>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="50"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="50"/>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="50"/>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="50"/>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="50"/>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="50"/>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="50"/>
+      <c r="B67" s="45"/>
+      <c r="C67" s="45"/>
+      <c r="D67" s="45"/>
+      <c r="E67" s="45"/>
+      <c r="F67" s="45"/>
+      <c r="G67" s="45"/>
+      <c r="H67" s="45"/>
+      <c r="I67" s="45"/>
+      <c r="J67" s="45"/>
+      <c r="K67" s="45"/>
+      <c r="L67" s="45"/>
+      <c r="M67" s="45"/>
+      <c r="N67" s="45"/>
+      <c r="O67" s="45"/>
+      <c r="P67" s="45"/>
+      <c r="Q67" s="45"/>
+      <c r="R67" s="45"/>
+      <c r="S67" s="45"/>
+      <c r="T67" s="45"/>
+      <c r="U67" s="45"/>
+      <c r="V67" s="45"/>
+      <c r="W67" s="46"/>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A68" s="37"/>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A69" s="37"/>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A70" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A48:W49"/>
-    <mergeCell ref="A50:W50"/>
+    <mergeCell ref="A65:W66"/>
+    <mergeCell ref="A67:W67"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A13:W14"/>
-    <mergeCell ref="A16:W16"/>
-    <mergeCell ref="A17:K47"/>
-    <mergeCell ref="L17:W47"/>
+    <mergeCell ref="A4:W4"/>
+    <mergeCell ref="A6:W7"/>
+    <mergeCell ref="A9:W9"/>
+    <mergeCell ref="A10:W63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -4381,7 +5541,7 @@
     <col min="9" max="14" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -4425,7 +5585,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -4469,7 +5629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -4513,7 +5673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -4557,7 +5717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -4601,7 +5761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -4645,7 +5805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -4689,7 +5849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -4733,7 +5893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -4777,7 +5937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -4821,7 +5981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -4865,7 +6025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -4909,7 +6069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -4953,7 +6113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -4997,7 +6157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -5050,7 +6210,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:Z15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -5061,7 +6221,7 @@
     <col min="9" max="26" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -5141,7 +6301,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -5221,7 +6381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -5301,7 +6461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -5381,7 +6541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -5461,7 +6621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -5541,7 +6701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -5621,7 +6781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -5701,7 +6861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -5781,7 +6941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -5861,7 +7021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -5941,7 +7101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -6021,7 +7181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -6101,7 +7261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -6181,7 +7341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -6270,7 +7430,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:AL15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -6281,7 +7441,7 @@
     <col min="9" max="38" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -6397,7 +7557,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -6513,7 +7673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -6629,7 +7789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -6745,7 +7905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -6861,7 +8021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -6977,7 +8137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -7093,7 +8253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -7209,7 +8369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -7325,7 +8485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -7441,7 +8601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -7557,7 +8717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -7673,7 +8833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -7789,7 +8949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -7905,7 +9065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -8030,7 +9190,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:W15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -8041,7 +9201,7 @@
     <col min="9" max="23" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -8112,7 +9272,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -8183,7 +9343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -8254,7 +9414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -8325,7 +9485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -8396,7 +9556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -8467,7 +9627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -8538,7 +9698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -8609,7 +9769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -8680,7 +9840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -8751,7 +9911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -8822,7 +9982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -8893,7 +10053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -8964,7 +10124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -9035,7 +10195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -9115,7 +10275,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:T15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -9126,7 +10286,7 @@
     <col min="9" max="20" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -9188,7 +10348,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -9250,7 +10410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -9312,7 +10472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -9374,7 +10534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -9436,7 +10596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -9498,7 +10658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -9560,7 +10720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -9622,7 +10782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -9684,7 +10844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -9746,7 +10906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -9808,7 +10968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -9870,7 +11030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -9932,7 +11092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -9994,7 +11154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -10065,7 +11225,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -10076,7 +11236,7 @@
     <col min="9" max="14" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -10120,7 +11280,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -10164,7 +11324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -10208,7 +11368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -10252,7 +11412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -10296,7 +11456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -10340,7 +11500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -10384,7 +11544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -10428,7 +11588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -10472,7 +11632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -10516,7 +11676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -10560,7 +11720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -10604,7 +11764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -10648,7 +11808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -10692,7 +11852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -10745,7 +11905,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:AC15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -10756,7 +11916,7 @@
     <col min="9" max="29" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -10845,7 +12005,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -10934,7 +12094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -11023,7 +12183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -11112,7 +12272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -11201,7 +12361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -11290,7 +12450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -11379,7 +12539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -11468,7 +12628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -11557,7 +12717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -11646,7 +12806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -11735,7 +12895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -11824,7 +12984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -11913,7 +13073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -12002,7 +13162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -12100,7 +13260,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:Q15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -12111,7 +13271,7 @@
     <col min="9" max="17" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -12164,7 +13324,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -12217,7 +13377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -12270,7 +13430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -12323,7 +13483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -12376,7 +13536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -12429,7 +13589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -12482,7 +13642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -12535,7 +13695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -12588,7 +13748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -12641,7 +13801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -12694,7 +13854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -12747,7 +13907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -12800,7 +13960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -12853,7 +14013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -12915,7 +14075,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:AX15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -12926,7 +14086,7 @@
     <col min="9" max="50" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -13078,7 +14238,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -13230,7 +14390,7 @@
         <v>2.6848384690431</v>
       </c>
     </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -13382,7 +14542,7 @@
         <v>5.3701772747994001</v>
       </c>
     </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -13534,7 +14694,7 @@
         <v>2.9797823177159999</v>
       </c>
     </row>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -13686,7 +14846,7 @@
         <v>2.6756340736482001</v>
       </c>
     </row>
-    <row r="6" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -13838,7 +14998,7 @@
         <v>0.86283163971452004</v>
       </c>
     </row>
-    <row r="7" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -13990,7 +15150,7 @@
         <v>0.29787410980376</v>
       </c>
     </row>
-    <row r="8" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -14142,7 +15302,7 @@
         <v>0.43604304823044998</v>
       </c>
     </row>
-    <row r="9" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -14294,7 +15454,7 @@
         <v>17.072345688702999</v>
       </c>
     </row>
-    <row r="10" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -14446,7 +15606,7 @@
         <v>0.84021353934773002</v>
       </c>
     </row>
-    <row r="11" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -14598,7 +15758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -14750,7 +15910,7 @@
         <v>0.17299834559451999</v>
       </c>
     </row>
-    <row r="13" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -14902,7 +16062,7 @@
         <v>0.87208609646089996</v>
       </c>
     </row>
-    <row r="14" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -15054,7 +16214,7 @@
         <v>0.12587478563706</v>
       </c>
     </row>
-    <row r="15" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -15215,7 +16375,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -15226,7 +16386,7 @@
     <col min="9" max="14" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -15270,7 +16430,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -15314,7 +16474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -15358,7 +16518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -15402,7 +16562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -15446,7 +16606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -15490,7 +16650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -15534,7 +16694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -15578,7 +16738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -15622,7 +16782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -15666,7 +16826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -15710,7 +16870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -15754,7 +16914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -15798,7 +16958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -15842,7 +17002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -15895,13 +17055,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C160"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="130" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -15912,8 +17072,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -15923,8 +17083,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="11"/>
       <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
@@ -15932,8 +17092,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="11"/>
       <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
@@ -15941,8 +17101,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="11"/>
       <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
@@ -15950,8 +17110,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="11"/>
       <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
@@ -15959,8 +17119,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="10"/>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="11"/>
       <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
@@ -15968,8 +17128,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="11"/>
       <c r="B8" s="3" t="s">
         <v>16</v>
       </c>
@@ -15977,8 +17137,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="11"/>
       <c r="B9" s="3" t="s">
         <v>18</v>
       </c>
@@ -15986,8 +17146,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="10"/>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="11"/>
       <c r="B10" s="3" t="s">
         <v>20</v>
       </c>
@@ -15995,8 +17155,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="10"/>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="11"/>
       <c r="B11" s="3" t="s">
         <v>22</v>
       </c>
@@ -16004,8 +17164,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="11"/>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
@@ -16013,8 +17173,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="10"/>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="11"/>
       <c r="B13" s="3" t="s">
         <v>26</v>
       </c>
@@ -16022,8 +17182,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="10"/>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="11"/>
       <c r="B14" s="3" t="s">
         <v>28</v>
       </c>
@@ -16031,8 +17191,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="10"/>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="11"/>
       <c r="B15" s="3" t="s">
         <v>30</v>
       </c>
@@ -16040,8 +17200,8 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="10"/>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="11"/>
       <c r="B16" s="3" t="s">
         <v>32</v>
       </c>
@@ -16049,8 +17209,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="12"/>
       <c r="B17" s="5" t="s">
         <v>34</v>
       </c>
@@ -16058,20 +17218,20 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+    <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-    </row>
-    <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+    </row>
+    <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="10" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -16081,8 +17241,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="10"/>
       <c r="B21" s="3" t="s">
         <v>40</v>
       </c>
@@ -16090,7 +17250,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="9"/>
       <c r="B22" s="5" t="s">
         <v>42</v>
@@ -16099,8 +17259,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="11" t="s">
         <v>44</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -16110,8 +17270,8 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="11"/>
       <c r="B24" s="3" t="s">
         <v>47</v>
       </c>
@@ -16119,8 +17279,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="10"/>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="11"/>
       <c r="B25" s="3" t="s">
         <v>49</v>
       </c>
@@ -16128,8 +17288,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="10"/>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="11"/>
       <c r="B26" s="3" t="s">
         <v>51</v>
       </c>
@@ -16137,8 +17297,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="10"/>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="11"/>
       <c r="B27" s="3" t="s">
         <v>53</v>
       </c>
@@ -16146,8 +17306,8 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="10"/>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="11"/>
       <c r="B28" s="3" t="s">
         <v>55</v>
       </c>
@@ -16155,8 +17315,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="10"/>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="11"/>
       <c r="B29" s="3" t="s">
         <v>57</v>
       </c>
@@ -16164,8 +17324,8 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="10"/>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="11"/>
       <c r="B30" s="3" t="s">
         <v>59</v>
       </c>
@@ -16173,8 +17333,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="10"/>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="11"/>
       <c r="B31" s="3" t="s">
         <v>61</v>
       </c>
@@ -16182,8 +17342,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="10"/>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="11"/>
       <c r="B32" s="3" t="s">
         <v>63</v>
       </c>
@@ -16191,8 +17351,8 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="10"/>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="11"/>
       <c r="B33" s="3" t="s">
         <v>65</v>
       </c>
@@ -16200,8 +17360,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="10"/>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="11"/>
       <c r="B34" s="3" t="s">
         <v>67</v>
       </c>
@@ -16209,8 +17369,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="10"/>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="11"/>
       <c r="B35" s="3" t="s">
         <v>69</v>
       </c>
@@ -16218,8 +17378,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="10"/>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="11"/>
       <c r="B36" s="3" t="s">
         <v>71</v>
       </c>
@@ -16227,8 +17387,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="10"/>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="11"/>
       <c r="B37" s="3" t="s">
         <v>73</v>
       </c>
@@ -16236,8 +17396,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="10"/>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="11"/>
       <c r="B38" s="3" t="s">
         <v>75</v>
       </c>
@@ -16245,8 +17405,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="10"/>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="11"/>
       <c r="B39" s="3" t="s">
         <v>77</v>
       </c>
@@ -16254,8 +17414,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="10"/>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="11"/>
       <c r="B40" s="3" t="s">
         <v>79</v>
       </c>
@@ -16263,8 +17423,8 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="10"/>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="11"/>
       <c r="B41" s="3" t="s">
         <v>81</v>
       </c>
@@ -16272,8 +17432,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="10"/>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="11"/>
       <c r="B42" s="3" t="s">
         <v>83</v>
       </c>
@@ -16281,8 +17441,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="10"/>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="11"/>
       <c r="B43" s="3" t="s">
         <v>85</v>
       </c>
@@ -16290,8 +17450,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="11"/>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="12"/>
       <c r="B44" s="5" t="s">
         <v>87</v>
       </c>
@@ -16299,8 +17459,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="14" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="10" t="s">
         <v>47</v>
       </c>
       <c r="B45" s="3" t="s">
@@ -16310,8 +17470,8 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="14"/>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="10"/>
       <c r="B46" s="3" t="s">
         <v>91</v>
       </c>
@@ -16319,8 +17479,8 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="14"/>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="10"/>
       <c r="B47" s="3" t="s">
         <v>93</v>
       </c>
@@ -16328,7 +17488,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="9"/>
       <c r="B48" s="5" t="s">
         <v>95</v>
@@ -16337,8 +17497,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="14" t="s">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="10" t="s">
         <v>49</v>
       </c>
       <c r="B49" s="3" t="s">
@@ -16348,8 +17508,8 @@
         <v>97</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="14"/>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="10"/>
       <c r="B50" s="3" t="s">
         <v>98</v>
       </c>
@@ -16357,8 +17517,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="14"/>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="10"/>
       <c r="B51" s="3" t="s">
         <v>100</v>
       </c>
@@ -16366,8 +17526,8 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="14"/>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="10"/>
       <c r="B52" s="3" t="s">
         <v>102</v>
       </c>
@@ -16375,7 +17535,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="9"/>
       <c r="B53" s="5" t="s">
         <v>104</v>
@@ -16384,8 +17544,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="14" t="s">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="10" t="s">
         <v>51</v>
       </c>
       <c r="B54" s="3" t="s">
@@ -16395,8 +17555,8 @@
         <v>106</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="14"/>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" s="10"/>
       <c r="B55" s="3" t="s">
         <v>107</v>
       </c>
@@ -16404,7 +17564,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="9"/>
       <c r="B56" s="5" t="s">
         <v>109</v>
@@ -16413,8 +17573,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="14" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" s="10" t="s">
         <v>53</v>
       </c>
       <c r="B57" s="3" t="s">
@@ -16424,8 +17584,8 @@
         <v>111</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="14"/>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" s="10"/>
       <c r="B58" s="3" t="s">
         <v>112</v>
       </c>
@@ -16433,8 +17593,8 @@
         <v>113</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="14"/>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" s="10"/>
       <c r="B59" s="3" t="s">
         <v>114</v>
       </c>
@@ -16442,8 +17602,8 @@
         <v>115</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="14"/>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" s="10"/>
       <c r="B60" s="3" t="s">
         <v>116</v>
       </c>
@@ -16451,8 +17611,8 @@
         <v>117</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="14"/>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" s="10"/>
       <c r="B61" s="3" t="s">
         <v>118</v>
       </c>
@@ -16460,7 +17620,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="9"/>
       <c r="B62" s="5" t="s">
         <v>120</v>
@@ -16469,8 +17629,8 @@
         <v>54</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="14" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" s="10" t="s">
         <v>55</v>
       </c>
       <c r="B63" s="3" t="s">
@@ -16480,8 +17640,8 @@
         <v>122</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="14"/>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" s="10"/>
       <c r="B64" s="3" t="s">
         <v>123</v>
       </c>
@@ -16489,7 +17649,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="9"/>
       <c r="B65" s="5" t="s">
         <v>125</v>
@@ -16498,8 +17658,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="14" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" s="10" t="s">
         <v>57</v>
       </c>
       <c r="B66" s="3" t="s">
@@ -16509,8 +17669,8 @@
         <v>127</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="14"/>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" s="10"/>
       <c r="B67" s="3" t="s">
         <v>128</v>
       </c>
@@ -16518,8 +17678,8 @@
         <v>129</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="14"/>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" s="10"/>
       <c r="B68" s="3" t="s">
         <v>130</v>
       </c>
@@ -16527,8 +17687,8 @@
         <v>131</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="14"/>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" s="10"/>
       <c r="B69" s="3" t="s">
         <v>132</v>
       </c>
@@ -16536,8 +17696,8 @@
         <v>133</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="14"/>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" s="10"/>
       <c r="B70" s="3" t="s">
         <v>134</v>
       </c>
@@ -16545,8 +17705,8 @@
         <v>135</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="14"/>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" s="10"/>
       <c r="B71" s="3" t="s">
         <v>136</v>
       </c>
@@ -16554,8 +17714,8 @@
         <v>137</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="14"/>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" s="10"/>
       <c r="B72" s="3" t="s">
         <v>138</v>
       </c>
@@ -16563,8 +17723,8 @@
         <v>139</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="14"/>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73" s="10"/>
       <c r="B73" s="3" t="s">
         <v>140</v>
       </c>
@@ -16572,8 +17732,8 @@
         <v>141</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="14"/>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" s="10"/>
       <c r="B74" s="3" t="s">
         <v>142</v>
       </c>
@@ -16581,8 +17741,8 @@
         <v>143</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="14"/>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" s="10"/>
       <c r="B75" s="3" t="s">
         <v>144</v>
       </c>
@@ -16590,8 +17750,8 @@
         <v>145</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="14"/>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76" s="10"/>
       <c r="B76" s="3" t="s">
         <v>146</v>
       </c>
@@ -16599,8 +17759,8 @@
         <v>147</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="14"/>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" s="10"/>
       <c r="B77" s="3" t="s">
         <v>148</v>
       </c>
@@ -16608,8 +17768,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="14"/>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78" s="10"/>
       <c r="B78" s="3" t="s">
         <v>150</v>
       </c>
@@ -16617,8 +17777,8 @@
         <v>151</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="14"/>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A79" s="10"/>
       <c r="B79" s="3" t="s">
         <v>152</v>
       </c>
@@ -16626,7 +17786,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="9"/>
       <c r="B80" s="5" t="s">
         <v>154</v>
@@ -16635,8 +17795,8 @@
         <v>58</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="14" t="s">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A81" s="10" t="s">
         <v>59</v>
       </c>
       <c r="B81" s="3" t="s">
@@ -16646,8 +17806,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="14"/>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A82" s="10"/>
       <c r="B82" s="3" t="s">
         <v>157</v>
       </c>
@@ -16655,8 +17815,8 @@
         <v>158</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="14"/>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83" s="10"/>
       <c r="B83" s="3" t="s">
         <v>159</v>
       </c>
@@ -16664,8 +17824,8 @@
         <v>160</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="14"/>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84" s="10"/>
       <c r="B84" s="3" t="s">
         <v>161</v>
       </c>
@@ -16673,8 +17833,8 @@
         <v>162</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="14"/>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A85" s="10"/>
       <c r="B85" s="3" t="s">
         <v>163</v>
       </c>
@@ -16682,8 +17842,8 @@
         <v>164</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="14"/>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86" s="10"/>
       <c r="B86" s="3" t="s">
         <v>165</v>
       </c>
@@ -16691,8 +17851,8 @@
         <v>166</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="14"/>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A87" s="10"/>
       <c r="B87" s="3" t="s">
         <v>167</v>
       </c>
@@ -16700,8 +17860,8 @@
         <v>168</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="14"/>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A88" s="10"/>
       <c r="B88" s="3" t="s">
         <v>169</v>
       </c>
@@ -16709,8 +17869,8 @@
         <v>170</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="14"/>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A89" s="10"/>
       <c r="B89" s="3" t="s">
         <v>171</v>
       </c>
@@ -16718,8 +17878,8 @@
         <v>172</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="14"/>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A90" s="10"/>
       <c r="B90" s="3" t="s">
         <v>173</v>
       </c>
@@ -16727,8 +17887,8 @@
         <v>174</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="14"/>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A91" s="10"/>
       <c r="B91" s="3" t="s">
         <v>175</v>
       </c>
@@ -16736,8 +17896,8 @@
         <v>176</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="14"/>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A92" s="10"/>
       <c r="B92" s="3" t="s">
         <v>177</v>
       </c>
@@ -16745,8 +17905,8 @@
         <v>178</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="14"/>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A93" s="10"/>
       <c r="B93" s="3" t="s">
         <v>179</v>
       </c>
@@ -16754,8 +17914,8 @@
         <v>180</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="14"/>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A94" s="10"/>
       <c r="B94" s="3" t="s">
         <v>181</v>
       </c>
@@ -16763,7 +17923,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="9"/>
       <c r="B95" s="5" t="s">
         <v>183</v>
@@ -16772,8 +17932,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="14" t="s">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A96" s="10" t="s">
         <v>61</v>
       </c>
       <c r="B96" s="3" t="s">
@@ -16783,7 +17943,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="9"/>
       <c r="B97" s="5" t="s">
         <v>186</v>
@@ -16792,8 +17952,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="14" t="s">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A98" s="10" t="s">
         <v>63</v>
       </c>
       <c r="B98" s="3" t="s">
@@ -16803,8 +17963,8 @@
         <v>188</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="14"/>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A99" s="10"/>
       <c r="B99" s="3" t="s">
         <v>189</v>
       </c>
@@ -16812,8 +17972,8 @@
         <v>190</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="14"/>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A100" s="10"/>
       <c r="B100" s="3" t="s">
         <v>191</v>
       </c>
@@ -16821,8 +17981,8 @@
         <v>192</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="14"/>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A101" s="10"/>
       <c r="B101" s="3" t="s">
         <v>193</v>
       </c>
@@ -16830,8 +17990,8 @@
         <v>194</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="14"/>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A102" s="10"/>
       <c r="B102" s="3" t="s">
         <v>195</v>
       </c>
@@ -16839,7 +17999,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="9"/>
       <c r="B103" s="5" t="s">
         <v>197</v>
@@ -16848,8 +18008,8 @@
         <v>64</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="14" t="s">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A104" s="10" t="s">
         <v>65</v>
       </c>
       <c r="B104" s="3" t="s">
@@ -16859,8 +18019,8 @@
         <v>199</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="14"/>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A105" s="10"/>
       <c r="B105" s="3" t="s">
         <v>200</v>
       </c>
@@ -16868,8 +18028,8 @@
         <v>201</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="14"/>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A106" s="10"/>
       <c r="B106" s="3" t="s">
         <v>202</v>
       </c>
@@ -16877,8 +18037,8 @@
         <v>203</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="14"/>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A107" s="10"/>
       <c r="B107" s="3" t="s">
         <v>204</v>
       </c>
@@ -16886,8 +18046,8 @@
         <v>205</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="14"/>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A108" s="10"/>
       <c r="B108" s="3" t="s">
         <v>206</v>
       </c>
@@ -16895,8 +18055,8 @@
         <v>207</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="14"/>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A109" s="10"/>
       <c r="B109" s="3" t="s">
         <v>208</v>
       </c>
@@ -16904,8 +18064,8 @@
         <v>209</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="14"/>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A110" s="10"/>
       <c r="B110" s="3" t="s">
         <v>210</v>
       </c>
@@ -16913,8 +18073,8 @@
         <v>211</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="14"/>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A111" s="10"/>
       <c r="B111" s="3" t="s">
         <v>212</v>
       </c>
@@ -16922,8 +18082,8 @@
         <v>213</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="14"/>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A112" s="10"/>
       <c r="B112" s="3" t="s">
         <v>214</v>
       </c>
@@ -16931,7 +18091,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="9"/>
       <c r="B113" s="5" t="s">
         <v>216</v>
@@ -16940,8 +18100,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="14" t="s">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A114" s="10" t="s">
         <v>67</v>
       </c>
       <c r="B114" s="3" t="s">
@@ -16951,8 +18111,8 @@
         <v>218</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="14"/>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A115" s="10"/>
       <c r="B115" s="3" t="s">
         <v>219</v>
       </c>
@@ -16960,8 +18120,8 @@
         <v>220</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="14"/>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A116" s="10"/>
       <c r="B116" s="3" t="s">
         <v>221</v>
       </c>
@@ -16969,8 +18129,8 @@
         <v>222</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="14"/>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A117" s="10"/>
       <c r="B117" s="3" t="s">
         <v>223</v>
       </c>
@@ -16978,7 +18138,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="9"/>
       <c r="B118" s="5" t="s">
         <v>225</v>
@@ -16987,8 +18147,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="14" t="s">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A119" s="10" t="s">
         <v>69</v>
       </c>
       <c r="B119" s="3" t="s">
@@ -16998,8 +18158,8 @@
         <v>227</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="14"/>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A120" s="10"/>
       <c r="B120" s="3" t="s">
         <v>228</v>
       </c>
@@ -17007,8 +18167,8 @@
         <v>229</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="14"/>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A121" s="10"/>
       <c r="B121" s="3" t="s">
         <v>230</v>
       </c>
@@ -17016,7 +18176,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" s="9"/>
       <c r="B122" s="5" t="s">
         <v>232</v>
@@ -17025,8 +18185,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="14" t="s">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A123" s="10" t="s">
         <v>71</v>
       </c>
       <c r="B123" s="3" t="s">
@@ -17036,7 +18196,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="9"/>
       <c r="B124" s="5" t="s">
         <v>235</v>
@@ -17045,8 +18205,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" s="14" t="s">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A125" s="10" t="s">
         <v>73</v>
       </c>
       <c r="B125" s="3" t="s">
@@ -17056,8 +18216,8 @@
         <v>237</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" s="14"/>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A126" s="10"/>
       <c r="B126" s="3" t="s">
         <v>238</v>
       </c>
@@ -17065,8 +18225,8 @@
         <v>239</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" s="14"/>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A127" s="10"/>
       <c r="B127" s="3" t="s">
         <v>240</v>
       </c>
@@ -17074,8 +18234,8 @@
         <v>241</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" s="14"/>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A128" s="10"/>
       <c r="B128" s="3" t="s">
         <v>242</v>
       </c>
@@ -17083,8 +18243,8 @@
         <v>243</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" s="14"/>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A129" s="10"/>
       <c r="B129" s="3" t="s">
         <v>244</v>
       </c>
@@ -17092,8 +18252,8 @@
         <v>245</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" s="14"/>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A130" s="10"/>
       <c r="B130" s="3" t="s">
         <v>246</v>
       </c>
@@ -17101,7 +18261,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="9"/>
       <c r="B131" s="5" t="s">
         <v>248</v>
@@ -17110,8 +18270,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" s="14" t="s">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A132" s="10" t="s">
         <v>75</v>
       </c>
       <c r="B132" s="3" t="s">
@@ -17121,8 +18281,8 @@
         <v>250</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" s="14"/>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A133" s="10"/>
       <c r="B133" s="3" t="s">
         <v>251</v>
       </c>
@@ -17130,7 +18290,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="9"/>
       <c r="B134" s="5" t="s">
         <v>253</v>
@@ -17139,8 +18299,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" s="14" t="s">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A135" s="10" t="s">
         <v>77</v>
       </c>
       <c r="B135" s="3" t="s">
@@ -17150,8 +18310,8 @@
         <v>255</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" s="14"/>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A136" s="10"/>
       <c r="B136" s="3" t="s">
         <v>256</v>
       </c>
@@ -17159,8 +18319,8 @@
         <v>257</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" s="14"/>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A137" s="10"/>
       <c r="B137" s="3" t="s">
         <v>258</v>
       </c>
@@ -17168,8 +18328,8 @@
         <v>259</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" s="14"/>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A138" s="10"/>
       <c r="B138" s="3" t="s">
         <v>260</v>
       </c>
@@ -17177,8 +18337,8 @@
         <v>261</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" s="14"/>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A139" s="10"/>
       <c r="B139" s="3" t="s">
         <v>262</v>
       </c>
@@ -17186,8 +18346,8 @@
         <v>263</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" s="14"/>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A140" s="10"/>
       <c r="B140" s="3" t="s">
         <v>264</v>
       </c>
@@ -17195,8 +18355,8 @@
         <v>265</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" s="14"/>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A141" s="10"/>
       <c r="B141" s="3" t="s">
         <v>266</v>
       </c>
@@ -17204,8 +18364,8 @@
         <v>267</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" s="14"/>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A142" s="10"/>
       <c r="B142" s="3" t="s">
         <v>268</v>
       </c>
@@ -17213,8 +18373,8 @@
         <v>269</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" s="14"/>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A143" s="10"/>
       <c r="B143" s="3" t="s">
         <v>270</v>
       </c>
@@ -17222,8 +18382,8 @@
         <v>271</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" s="14"/>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A144" s="10"/>
       <c r="B144" s="3" t="s">
         <v>272</v>
       </c>
@@ -17231,8 +18391,8 @@
         <v>273</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" s="14"/>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A145" s="10"/>
       <c r="B145" s="3" t="s">
         <v>274</v>
       </c>
@@ -17240,8 +18400,8 @@
         <v>275</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" s="14"/>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A146" s="10"/>
       <c r="B146" s="3" t="s">
         <v>276</v>
       </c>
@@ -17249,8 +18409,8 @@
         <v>277</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147" s="14"/>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A147" s="10"/>
       <c r="B147" s="3" t="s">
         <v>278</v>
       </c>
@@ -17258,7 +18418,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" s="9"/>
       <c r="B148" s="5" t="s">
         <v>280</v>
@@ -17267,8 +18427,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" s="14" t="s">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A149" s="10" t="s">
         <v>79</v>
       </c>
       <c r="B149" s="3" t="s">
@@ -17278,7 +18438,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" s="9"/>
       <c r="B150" s="5" t="s">
         <v>283</v>
@@ -17287,8 +18447,8 @@
         <v>80</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151" s="14" t="s">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A151" s="10" t="s">
         <v>284</v>
       </c>
       <c r="B151" s="3" t="s">
@@ -17298,8 +18458,8 @@
         <v>286</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152" s="14"/>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A152" s="10"/>
       <c r="B152" s="3" t="s">
         <v>287</v>
       </c>
@@ -17307,8 +18467,8 @@
         <v>288</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" s="14"/>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A153" s="10"/>
       <c r="B153" s="3" t="s">
         <v>289</v>
       </c>
@@ -17316,8 +18476,8 @@
         <v>290</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" s="14"/>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A154" s="10"/>
       <c r="B154" s="3" t="s">
         <v>291</v>
       </c>
@@ -17325,7 +18485,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" s="9"/>
       <c r="B155" s="5" t="s">
         <v>293</v>
@@ -17334,8 +18494,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" s="14" t="s">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A156" s="10" t="s">
         <v>83</v>
       </c>
       <c r="B156" s="3" t="s">
@@ -17345,7 +18505,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="9"/>
       <c r="B157" s="5" t="s">
         <v>296</v>
@@ -17354,8 +18514,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A158" s="14" t="s">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A158" s="10" t="s">
         <v>85</v>
       </c>
       <c r="B158" s="3" t="s">
@@ -17365,7 +18525,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" s="9"/>
       <c r="B159" s="5" t="s">
         <v>299</v>
@@ -17374,7 +18534,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" s="9" t="s">
         <v>87</v>
       </c>
@@ -17388,32 +18548,32 @@
   </sheetData>
   <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="26">
+    <mergeCell ref="A1"/>
+    <mergeCell ref="A2:A17"/>
+    <mergeCell ref="A18:C19"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A23:A44"/>
+    <mergeCell ref="A45:A48"/>
+    <mergeCell ref="A49:A53"/>
+    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="A57:A62"/>
+    <mergeCell ref="A63:A65"/>
+    <mergeCell ref="A66:A80"/>
+    <mergeCell ref="A81:A95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A98:A103"/>
+    <mergeCell ref="A104:A113"/>
+    <mergeCell ref="A114:A118"/>
+    <mergeCell ref="A119:A122"/>
+    <mergeCell ref="A123:A124"/>
+    <mergeCell ref="A125:A131"/>
+    <mergeCell ref="A132:A134"/>
     <mergeCell ref="A160"/>
     <mergeCell ref="A135:A148"/>
     <mergeCell ref="A149:A150"/>
     <mergeCell ref="A151:A155"/>
     <mergeCell ref="A156:A157"/>
     <mergeCell ref="A158:A159"/>
-    <mergeCell ref="A114:A118"/>
-    <mergeCell ref="A119:A122"/>
-    <mergeCell ref="A123:A124"/>
-    <mergeCell ref="A125:A131"/>
-    <mergeCell ref="A132:A134"/>
-    <mergeCell ref="A66:A80"/>
-    <mergeCell ref="A81:A95"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A98:A103"/>
-    <mergeCell ref="A104:A113"/>
-    <mergeCell ref="A45:A48"/>
-    <mergeCell ref="A49:A53"/>
-    <mergeCell ref="A54:A56"/>
-    <mergeCell ref="A57:A62"/>
-    <mergeCell ref="A63:A65"/>
-    <mergeCell ref="A1"/>
-    <mergeCell ref="A2:A17"/>
-    <mergeCell ref="A18:C19"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="A23:A44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17422,7 +18582,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:BA15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -17433,7 +18593,7 @@
     <col min="9" max="53" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -17594,7 +18754,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -17755,7 +18915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -17916,7 +19076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -18077,7 +19237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -18238,7 +19398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -18399,7 +19559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -18560,7 +19720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -18721,7 +19881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -18882,7 +20042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -19043,7 +20203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -19204,7 +20364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -19365,7 +20525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -19526,7 +20686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -19687,7 +20847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -19857,7 +21017,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:W15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -19868,7 +21028,7 @@
     <col min="9" max="23" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -19939,7 +21099,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -20010,7 +21170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -20081,7 +21241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -20152,7 +21312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -20223,7 +21383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -20294,7 +21454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -20365,7 +21525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -20436,7 +21596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -20507,7 +21667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -20578,7 +21738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -20649,7 +21809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -20720,7 +21880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -20791,7 +21951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -20862,7 +22022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -20942,7 +22102,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -20953,7 +22113,7 @@
     <col min="9" max="14" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -20997,7 +22157,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -21041,7 +22201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -21085,7 +22245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -21129,7 +22289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -21173,7 +22333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -21217,7 +22377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -21261,7 +22421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -21305,7 +22465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -21349,7 +22509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -21393,7 +22553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -21437,7 +22597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -21481,7 +22641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -21525,7 +22685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -21569,7 +22729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -21622,7 +22782,7 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -21633,7 +22793,7 @@
     <col min="9" max="14" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -21677,7 +22837,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -21721,7 +22881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -21765,7 +22925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -21809,7 +22969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -21853,7 +23013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -21897,7 +23057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -21941,7 +23101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -21985,7 +23145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -22029,7 +23189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -22073,7 +23233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -22117,7 +23277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -22161,7 +23321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -22205,7 +23365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -22249,7 +23409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -22302,7 +23462,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -22312,7 +23472,7 @@
     <col min="6" max="8" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -22338,7 +23498,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -22364,7 +23524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -22390,7 +23550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -22416,7 +23576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -22442,7 +23602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -22468,7 +23628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -22494,7 +23654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -22520,7 +23680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -22546,7 +23706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -22572,7 +23732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -22598,7 +23758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -22624,7 +23784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -22650,7 +23810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -22676,7 +23836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -22711,7 +23871,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CD15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -22735,7 +23895,7 @@
     <col min="80" max="82" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -22983,7 +24143,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="2" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -23228,7 +24388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -23473,7 +24633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -23718,7 +24878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -23963,7 +25123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -24208,7 +25368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -24453,7 +25613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -24698,7 +25858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -24943,7 +26103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -25188,7 +26348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -25433,7 +26593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -25678,7 +26838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -25923,7 +27083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -26168,7 +27328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:82" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -26422,7 +27582,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:T15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -26435,7 +27595,7 @@
     <col min="15" max="20" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -26497,7 +27657,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -26559,7 +27719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -26621,7 +27781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -26683,7 +27843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -26745,7 +27905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -26807,7 +27967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -26869,7 +28029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -26931,7 +28091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -26993,7 +28153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -27055,7 +28215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -27117,7 +28277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -27179,7 +28339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -27241,7 +28401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -27303,7 +28463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -27374,7 +28534,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:W15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -27385,7 +28545,7 @@
     <col min="9" max="23" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -27456,7 +28616,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -27527,7 +28687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -27598,7 +28758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -27669,7 +28829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -27740,7 +28900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -27811,7 +28971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -27882,7 +29042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -27953,7 +29113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -28024,7 +29184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -28095,7 +29255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -28166,7 +29326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -28237,7 +29397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -28308,7 +29468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -28379,7 +29539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -28459,7 +29619,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Q15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -28470,7 +29630,7 @@
     <col min="9" max="17" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -28523,7 +29683,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -28576,7 +29736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -28629,7 +29789,7 @@
         <v>2247.7064809663998</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -28682,7 +29842,7 @@
         <v>160.39647791185999</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -28735,7 +29895,7 @@
         <v>103.53670702992</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -28788,7 +29948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -28841,7 +30001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -28894,7 +30054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -28947,7 +30107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -29000,7 +30160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -29053,7 +30213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -29106,7 +30266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -29159,7 +30319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -29212,7 +30372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -29274,7 +30434,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Z15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -29285,7 +30445,7 @@
     <col min="9" max="26" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -29365,7 +30525,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -29445,7 +30605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -29525,7 +30685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -29605,7 +30765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -29685,7 +30845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -29765,7 +30925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -29845,7 +31005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -29925,7 +31085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -30005,7 +31165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -30085,7 +31245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -30165,7 +31325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -30245,7 +31405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -30325,7 +31485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -30405,7 +31565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -30494,7 +31654,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:Q15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -30505,7 +31665,7 @@
     <col min="9" max="17" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -30558,7 +31718,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -30611,7 +31771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -30664,7 +31824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -30717,7 +31877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -30770,7 +31930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -30823,7 +31983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -30876,7 +32036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -30929,7 +32089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -30982,7 +32142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -31035,7 +32195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -31088,7 +32248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -31141,7 +32301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -31194,7 +32354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -31247,7 +32407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
@@ -31309,7 +32469,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:BA15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -31320,7 +32480,7 @@
     <col min="9" max="53" width="9" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -31481,7 +32641,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>577</v>
       </c>
@@ -31642,7 +32802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>578</v>
       </c>
@@ -31803,7 +32963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>579</v>
       </c>
@@ -31964,7 +33124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>580</v>
       </c>
@@ -32125,7 +33285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>581</v>
       </c>
@@ -32286,7 +33446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>582</v>
       </c>
@@ -32447,7 +33607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>583</v>
       </c>
@@ -32608,7 +33768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>584</v>
       </c>
@@ -32769,7 +33929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>585</v>
       </c>
@@ -32930,7 +34090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>586</v>
       </c>
@@ -33091,7 +34251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>587</v>
       </c>
@@ -33252,7 +34412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>588</v>
       </c>
@@ -33413,7 +34573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>589</v>
       </c>
@@ -33574,7 +34734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>590</v>
       </c>
